--- a/song_records.xlsx
+++ b/song_records.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\73415\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22D5D34C-BB4A-4C2E-8F57-33F5AA093526}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B93B969B-27B4-4F4F-B42A-632F7BA9EA26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18870" windowHeight="6855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
-    <sheet name="歌曲彙總" sheetId="2" r:id="rId2"/>
+    <sheet name="歌曲彙總" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="576">
   <si>
     <t>id</t>
   </si>
@@ -51,1384 +51,1702 @@
     <t>https://www.youtube.com/watch?v=PZN1ns6OIyc</t>
   </si>
   <si>
+    <t>下一個天亮（zh32）</t>
+  </si>
+  <si>
+    <t>大笑之歌（zh1）</t>
+  </si>
+  <si>
+    <t>大番薯（hak1）</t>
+  </si>
+  <si>
+    <t>小幸運（zh26）</t>
+  </si>
+  <si>
+    <t>不可幸力（ja18）</t>
+  </si>
+  <si>
+    <t>不夠成熟（zh28）</t>
+  </si>
+  <si>
+    <t>分手後不要做朋友（zh29）</t>
+  </si>
+  <si>
+    <t>天黑黑（zh54）</t>
+  </si>
+  <si>
+    <t>太陽與地球（zh46）</t>
+  </si>
+  <si>
+    <t>太陽與地球（yue1）</t>
+  </si>
+  <si>
+    <t>水星記（zh47）</t>
+  </si>
+  <si>
+    <t>半句再見（zh4）</t>
+  </si>
+  <si>
+    <t>白日（ja21）</t>
+  </si>
+  <si>
+    <t>再會啦心愛的無緣的人（nan2）</t>
+  </si>
+  <si>
+    <t>因為單身的緣故（zh14）</t>
+  </si>
+  <si>
+    <t>在迦納共和國離婚（zh44）</t>
+  </si>
+  <si>
+    <t>她說（zh52）</t>
+  </si>
+  <si>
+    <t>如果我不知道（zh43）</t>
+  </si>
+  <si>
+    <t>年輪說（zh40）</t>
+  </si>
+  <si>
+    <t>有一種悲傷（zh34）</t>
+  </si>
+  <si>
+    <t>老鼠愛大米（zh31）</t>
+  </si>
+  <si>
+    <t>自導自演（zh45）</t>
+  </si>
+  <si>
+    <t>你就不要想起我（zh36）</t>
+  </si>
+  <si>
+    <t>別の人の彼女になったよ（ja24）</t>
+  </si>
+  <si>
+    <t>含淚跳恰恰（nan1）</t>
+  </si>
+  <si>
+    <t>我不配（zh30）</t>
+  </si>
+  <si>
+    <t>我不難過（zh11）</t>
+  </si>
+  <si>
+    <t>我在紐約打電話給你（zh9）</t>
+  </si>
+  <si>
+    <t>我的歌聲裡（zh49）</t>
+  </si>
+  <si>
+    <t>我是恁老爸（nan6）</t>
+  </si>
+  <si>
+    <t>我們不一樣（zh13）</t>
+  </si>
+  <si>
+    <t>我想我不會愛你（zh39）</t>
+  </si>
+  <si>
+    <t>我想要佔據你（zh56）</t>
+  </si>
+  <si>
+    <t>我會好好的（zh53）</t>
+  </si>
+  <si>
+    <t>我懷念的（zh12）</t>
+  </si>
+  <si>
+    <t>刻在我心底的名字（zh19）</t>
+  </si>
+  <si>
+    <t>孤獨的總和（zh6）</t>
+  </si>
+  <si>
+    <t>怪獣の花唄（ja16）</t>
+  </si>
+  <si>
+    <t>明明就（zh21）</t>
+  </si>
+  <si>
+    <t>東京フラッシュ（ja10）</t>
+  </si>
+  <si>
+    <t>知道（zh24）</t>
+  </si>
+  <si>
+    <t>雨愛（zh37）</t>
+  </si>
+  <si>
+    <t>変わらないもの（ja26）</t>
+  </si>
+  <si>
+    <t>革命道中（ja4）</t>
+  </si>
+  <si>
+    <t>香水（ja20）</t>
+  </si>
+  <si>
+    <t>香水（nan3）</t>
+  </si>
+  <si>
+    <t>修練愛情（zh57）</t>
+  </si>
+  <si>
+    <t>倒帶（zh23）</t>
+  </si>
+  <si>
+    <t>挪威的森林（zh7）</t>
+  </si>
+  <si>
+    <t>浪子回頭（nan4）</t>
+  </si>
+  <si>
+    <t>逆光（zh58）</t>
+  </si>
+  <si>
+    <t>逆さまの蝶（ja19）</t>
+  </si>
+  <si>
+    <t>鬼ノ宴(Demons Banquet)（ja7）</t>
+  </si>
+  <si>
+    <t>偽顏（ja12）</t>
+  </si>
+  <si>
+    <t>寂寞寂寞就好（zh22）</t>
+  </si>
+  <si>
+    <t>帶我走（zh51）</t>
+  </si>
+  <si>
+    <t>捲菸（zh18）</t>
+  </si>
+  <si>
+    <t>逢いたくていま（ja22）</t>
+  </si>
+  <si>
+    <t>喜劇收場（zh27）</t>
+  </si>
+  <si>
+    <t>幾分之幾（zh20）</t>
+  </si>
+  <si>
+    <t>渺小（zh38）</t>
+  </si>
+  <si>
+    <t>買你（zh8）</t>
+  </si>
+  <si>
+    <t>開始懂了（zh10）</t>
+  </si>
+  <si>
+    <t>微加幸福（zh15）</t>
+  </si>
+  <si>
+    <t>愛情怎麼了嗎（zh48）</t>
+  </si>
+  <si>
+    <t>愛過的樣子（zh42）</t>
+  </si>
+  <si>
+    <t>舅媽（zh50）</t>
+  </si>
+  <si>
+    <t>落雨聲（nan5）</t>
+  </si>
+  <si>
+    <t>路過人間（zh3）</t>
+  </si>
+  <si>
+    <t>遇見（zh55）</t>
+  </si>
+  <si>
+    <t>像天堂的懸崖（zh33）</t>
+  </si>
+  <si>
+    <t>夢醒時分（zh41）</t>
+  </si>
+  <si>
+    <t>慢冷（zh5）</t>
+  </si>
+  <si>
+    <t>踊り子（ja11）</t>
+  </si>
+  <si>
+    <t>曖昧（zh25）</t>
+  </si>
+  <si>
+    <t>藍（zh2）</t>
+  </si>
+  <si>
+    <t>聽見下雨的聲音（zh35）</t>
+  </si>
+  <si>
+    <t>體面（zh17）</t>
+  </si>
+  <si>
+    <t>ACT/アクト（ja1）</t>
+  </si>
+  <si>
+    <t>BAD GUY（en1）</t>
+  </si>
+  <si>
+    <t>Breathe（ko1）</t>
+  </si>
+  <si>
+    <t>Bunny Girl（ja5）</t>
+  </si>
+  <si>
+    <t>Bのリベンジ（ja32）</t>
+  </si>
+  <si>
+    <t>CoCo（en4）</t>
+  </si>
+  <si>
+    <t>Hero's Come Back!!（ja30）</t>
+  </si>
+  <si>
+    <t>i love you（en3）</t>
+  </si>
+  <si>
+    <t>IRIS OUT（ja3）</t>
+  </si>
+  <si>
+    <t>JANE DOE（ja2）</t>
+  </si>
+  <si>
+    <t>Miniskirt（ko2）</t>
+  </si>
+  <si>
+    <t>NIGHT DANCER（ja14）</t>
+  </si>
+  <si>
+    <t>Overdose（ja9）</t>
+  </si>
+  <si>
+    <t>Playground（en5）</t>
+  </si>
+  <si>
+    <t>Santé（zh16）</t>
+  </si>
+  <si>
+    <t>the WORLD（ja31）</t>
+  </si>
+  <si>
+    <t>wish you were gay（en2）</t>
+  </si>
+  <si>
+    <t>いのちの名前（ja27）</t>
+  </si>
+  <si>
+    <t>カタオモイ（ja13）</t>
+  </si>
+  <si>
+    <t>シンデレラボーイ（ja28）</t>
+  </si>
+  <si>
+    <t>たばこ（ja29）</t>
+  </si>
+  <si>
+    <t>どうせ無くなるだけ（ja15）</t>
+  </si>
+  <si>
+    <t>ドライフラワー（ja17）</t>
+  </si>
+  <si>
+    <t>なんか幸せ（ja25）</t>
+  </si>
+  <si>
+    <t>プロポーズ（ja6）</t>
+  </si>
+  <si>
+    <t>ホウキ雲（ja23）</t>
+  </si>
+  <si>
+    <t>ほろよい（ja8）</t>
+  </si>
+  <si>
+    <t>Cover</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
+  </si>
+  <si>
+    <t>7:16</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>17:34</t>
+  </si>
+  <si>
+    <t>21:56</t>
+  </si>
+  <si>
+    <t>26:23</t>
+  </si>
+  <si>
+    <t>32:29</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>33:52</t>
+  </si>
+  <si>
+    <t>34:58</t>
+  </si>
+  <si>
+    <t>37:38</t>
+  </si>
+  <si>
+    <t>40:59</t>
+  </si>
+  <si>
+    <t>42:09</t>
+  </si>
+  <si>
+    <t>44:43</t>
+  </si>
+  <si>
+    <t>47:01</t>
+  </si>
+  <si>
+    <t>52:08</t>
+  </si>
+  <si>
+    <t>57:34</t>
+  </si>
+  <si>
+    <t>觀眾唱</t>
+  </si>
+  <si>
+    <t>1:03:45</t>
+  </si>
+  <si>
+    <t>1:08:09</t>
+  </si>
+  <si>
+    <t>1:12:27</t>
+  </si>
+  <si>
+    <t>1:17:44</t>
+  </si>
+  <si>
+    <t>切歌</t>
+  </si>
+  <si>
+    <t>1:18:47</t>
+  </si>
+  <si>
+    <t>1:25:12</t>
+  </si>
+  <si>
+    <t>1:33:37</t>
+  </si>
+  <si>
+    <t>4:15:50</t>
+  </si>
+  <si>
+    <t>4:18:46</t>
+  </si>
+  <si>
+    <t>4:20:12</t>
+  </si>
+  <si>
+    <t>4:24:52</t>
+  </si>
+  <si>
+    <t>4:27:12</t>
+  </si>
+  <si>
+    <t>4:29:40</t>
+  </si>
+  <si>
+    <t>4:32:59</t>
+  </si>
+  <si>
+    <t>4:35:26</t>
+  </si>
+  <si>
+    <t>4:38:47</t>
+  </si>
+  <si>
+    <t>4:44:17</t>
+  </si>
+  <si>
+    <t>4:48:35</t>
+  </si>
+  <si>
+    <t>4:53:54</t>
+  </si>
+  <si>
+    <t>4:59:15</t>
+  </si>
+  <si>
+    <t>5:04:18</t>
+  </si>
+  <si>
+    <t>5:10:38</t>
+  </si>
+  <si>
+    <t>5:14:05</t>
+  </si>
+  <si>
+    <t>5:15:38</t>
+  </si>
+  <si>
+    <t>5:20:33</t>
+  </si>
+  <si>
+    <t>5:21:48</t>
+  </si>
+  <si>
+    <t>5:26:07</t>
+  </si>
+  <si>
+    <t>5:28:28</t>
+  </si>
+  <si>
+    <t>5:35:39</t>
+  </si>
+  <si>
+    <t>5:41:14</t>
+  </si>
+  <si>
+    <t>5:43:10</t>
+  </si>
+  <si>
+    <t>5:47:00</t>
+  </si>
+  <si>
+    <t>5:49:00</t>
+  </si>
+  <si>
+    <t>5:52:55</t>
+  </si>
+  <si>
+    <t>5:56:05</t>
+  </si>
+  <si>
+    <t>5:58:06</t>
+  </si>
+  <si>
+    <t>6:01:13</t>
+  </si>
+  <si>
+    <t>6:03:12</t>
+  </si>
+  <si>
+    <t>6:05:24</t>
+  </si>
+  <si>
+    <t>6:09:58</t>
+  </si>
+  <si>
+    <t>6:11:14</t>
+  </si>
+  <si>
+    <t>6:13:40</t>
+  </si>
+  <si>
+    <t>6:18:16</t>
+  </si>
+  <si>
+    <t>6:24:26</t>
+  </si>
+  <si>
+    <t>6:36:21</t>
+  </si>
+  <si>
+    <t>6:46:04</t>
+  </si>
+  <si>
+    <t>6:53:33</t>
+  </si>
+  <si>
+    <t>7:03:34</t>
+  </si>
+  <si>
+    <t>7:08:22</t>
+  </si>
+  <si>
+    <t>39:47</t>
+  </si>
+  <si>
+    <t>45:02</t>
+  </si>
+  <si>
+    <t>51:24</t>
+  </si>
+  <si>
+    <t>56:42</t>
+  </si>
+  <si>
+    <t>1:02:53</t>
+  </si>
+  <si>
+    <t>1:14:02</t>
+  </si>
+  <si>
+    <t>1:19:07</t>
+  </si>
+  <si>
+    <t>1:26:53</t>
+  </si>
+  <si>
+    <t>1:33:50</t>
+  </si>
+  <si>
+    <t>1:40:01</t>
+  </si>
+  <si>
+    <t>1:47:22</t>
+  </si>
+  <si>
+    <t>1:59:55</t>
+  </si>
+  <si>
+    <t>2:05:01</t>
+  </si>
+  <si>
+    <t>2:14:03</t>
+  </si>
+  <si>
+    <t>2:16:55</t>
+  </si>
+  <si>
+    <t>2:22:12</t>
+  </si>
+  <si>
+    <t>2:27:49</t>
+  </si>
+  <si>
+    <t>2:35:24</t>
+  </si>
+  <si>
+    <t>2:40:30</t>
+  </si>
+  <si>
+    <t>2:50:00</t>
+  </si>
+  <si>
+    <t>2:54:45</t>
+  </si>
+  <si>
+    <t>3:00:18</t>
+  </si>
+  <si>
+    <t>3:11:22</t>
+  </si>
+  <si>
+    <t>3:22:00</t>
+  </si>
+  <si>
+    <t>3:29:16</t>
+  </si>
+  <si>
+    <t>3:30:42</t>
+  </si>
+  <si>
+    <t>3:39:48</t>
+  </si>
+  <si>
+    <t>3:43:29</t>
+  </si>
+  <si>
+    <t>3:48:22</t>
+  </si>
+  <si>
+    <t>3:53:31</t>
+  </si>
+  <si>
+    <t>3:55:11</t>
+  </si>
+  <si>
+    <t>4:01:19</t>
+  </si>
+  <si>
+    <t>4:06:47</t>
+  </si>
+  <si>
+    <t>4:09:57</t>
+  </si>
+  <si>
+    <t>4:16:28</t>
+  </si>
+  <si>
+    <t>4:19:07</t>
+  </si>
+  <si>
+    <t>4:23:01</t>
+  </si>
+  <si>
+    <t>4:27:49</t>
+  </si>
+  <si>
+    <t>1:31:53</t>
+  </si>
+  <si>
+    <t>3:27:05</t>
+  </si>
+  <si>
+    <t>3:28:00</t>
+  </si>
+  <si>
+    <t>4:20:39</t>
+  </si>
+  <si>
+    <t>一支小雨傘（nan7）</t>
+  </si>
+  <si>
+    <t>8:47</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>25:09</t>
+  </si>
+  <si>
+    <t>25:49</t>
+  </si>
+  <si>
+    <t>29:05</t>
+  </si>
+  <si>
+    <t>33:29</t>
+  </si>
+  <si>
+    <t>40:42</t>
+  </si>
+  <si>
+    <t>45:40</t>
+  </si>
+  <si>
+    <t>47:26</t>
+  </si>
+  <si>
+    <t>50:58</t>
+  </si>
+  <si>
+    <t>52:33</t>
+  </si>
+  <si>
+    <t>改編</t>
+  </si>
+  <si>
+    <t>55:15</t>
+  </si>
+  <si>
+    <t>1:00:20</t>
+  </si>
+  <si>
+    <t>1:06:09</t>
+  </si>
+  <si>
+    <t>1:10:44</t>
+  </si>
+  <si>
+    <t>1:16:37</t>
+  </si>
+  <si>
+    <t>1:21:35</t>
+  </si>
+  <si>
+    <t>1:26:58</t>
+  </si>
+  <si>
+    <t>1:31:34</t>
+  </si>
+  <si>
+    <t>片段</t>
+  </si>
+  <si>
+    <t>1:36:36</t>
+  </si>
+  <si>
+    <t>1:37:35</t>
+  </si>
+  <si>
+    <t>1:43:06</t>
+  </si>
+  <si>
+    <t>1:47:01</t>
+  </si>
+  <si>
+    <t>1:54:59</t>
+  </si>
+  <si>
+    <t>開夾</t>
+  </si>
+  <si>
+    <t>2:03:06</t>
+  </si>
+  <si>
+    <t>2:07:16</t>
+  </si>
+  <si>
+    <t>2:11:07</t>
+  </si>
+  <si>
+    <t>2:11:50</t>
+  </si>
+  <si>
+    <t>27:28</t>
+  </si>
+  <si>
+    <t>32:40</t>
+  </si>
+  <si>
+    <t>34:45</t>
+  </si>
+  <si>
+    <t>37:49</t>
+  </si>
+  <si>
+    <t>42:49</t>
+  </si>
+  <si>
+    <t>47:34</t>
+  </si>
+  <si>
+    <t>53:10</t>
+  </si>
+  <si>
+    <t>1:01:05</t>
+  </si>
+  <si>
+    <t>1:04:58</t>
+  </si>
+  <si>
+    <t>1:09:59</t>
+  </si>
+  <si>
+    <t>1:17:22</t>
+  </si>
+  <si>
+    <t>2:48:50</t>
+  </si>
+  <si>
+    <t>3:02:49</t>
+  </si>
+  <si>
+    <t>3:06:56</t>
+  </si>
+  <si>
+    <t>3:18:02</t>
+  </si>
+  <si>
+    <t>3:22:40</t>
+  </si>
+  <si>
+    <t>3:28:24</t>
+  </si>
+  <si>
+    <t>3:35:00</t>
+  </si>
+  <si>
+    <t>3:41:11</t>
+  </si>
+  <si>
+    <t>3:42:35</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bZn2uiXpNvE?t=13311</t>
+  </si>
+  <si>
+    <t>3:41:51</t>
+  </si>
+  <si>
+    <t>知花</t>
+  </si>
+  <si>
+    <t>合唱</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G_5bOFykGPs</t>
+  </si>
+  <si>
+    <t>福栗, 真理果</t>
+  </si>
+  <si>
+    <t>Cover, 合唱</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zbOsJbnkhyk</t>
+  </si>
+  <si>
+    <t>神崎アルファ</t>
+  </si>
+  <si>
+    <t>zh1</t>
+  </si>
+  <si>
+    <t>en1</t>
+  </si>
+  <si>
+    <t>ja1</t>
+  </si>
+  <si>
+    <t>zh2</t>
+  </si>
+  <si>
+    <t>zh3</t>
+  </si>
+  <si>
+    <t>zh4</t>
+  </si>
+  <si>
+    <t>zh5</t>
+  </si>
+  <si>
+    <t>ja2</t>
+  </si>
+  <si>
+    <t>ja3</t>
+  </si>
+  <si>
+    <t>ja4</t>
+  </si>
+  <si>
+    <t>nan1</t>
+  </si>
+  <si>
+    <t>zh6</t>
+  </si>
+  <si>
+    <t>zh7</t>
+  </si>
+  <si>
+    <t>zh8</t>
+  </si>
+  <si>
+    <t>zh9</t>
+  </si>
+  <si>
+    <t>zh10</t>
+  </si>
+  <si>
+    <t>zh11</t>
+  </si>
+  <si>
+    <t>zh12</t>
+  </si>
+  <si>
+    <t>nan2</t>
+  </si>
+  <si>
+    <t>zh13</t>
+  </si>
+  <si>
+    <t>zh14</t>
+  </si>
+  <si>
+    <t>ja5</t>
+  </si>
+  <si>
+    <t>ja6</t>
+  </si>
+  <si>
+    <t>ja7</t>
+  </si>
+  <si>
+    <t>ja8</t>
+  </si>
+  <si>
+    <t>ja9</t>
+  </si>
+  <si>
+    <t>ja10</t>
+  </si>
+  <si>
+    <t>ja11</t>
+  </si>
+  <si>
+    <t>en2</t>
+  </si>
+  <si>
+    <t>en3</t>
+  </si>
+  <si>
+    <t>zh15</t>
+  </si>
+  <si>
+    <t>en4</t>
+  </si>
+  <si>
+    <t>ja12</t>
+  </si>
+  <si>
+    <t>ja13</t>
+  </si>
+  <si>
+    <t>ja14</t>
+  </si>
+  <si>
+    <t>ja15</t>
+  </si>
+  <si>
+    <t>ja16</t>
+  </si>
+  <si>
+    <t>ja17</t>
+  </si>
+  <si>
+    <t>zh16</t>
+  </si>
+  <si>
+    <t>ja18</t>
+  </si>
+  <si>
+    <t>ja19</t>
+  </si>
+  <si>
+    <t>zh17</t>
+  </si>
+  <si>
+    <t>nan3</t>
+  </si>
+  <si>
+    <t>ja20</t>
+  </si>
+  <si>
+    <t>zh18</t>
+  </si>
+  <si>
+    <t>nan4</t>
+  </si>
+  <si>
+    <t>zh19</t>
+  </si>
+  <si>
+    <t>zh20</t>
+  </si>
+  <si>
+    <t>zh21</t>
+  </si>
+  <si>
+    <t>zh22</t>
+  </si>
+  <si>
+    <t>zh23</t>
+  </si>
+  <si>
+    <t>zh24</t>
+  </si>
+  <si>
+    <t>zh25</t>
+  </si>
+  <si>
+    <t>zh26</t>
+  </si>
+  <si>
+    <t>zh27</t>
+  </si>
+  <si>
+    <t>zh28</t>
+  </si>
+  <si>
+    <t>zh29</t>
+  </si>
+  <si>
+    <t>zh30</t>
+  </si>
+  <si>
+    <t>zh31</t>
+  </si>
+  <si>
+    <t>zh32</t>
+  </si>
+  <si>
+    <t>zh33</t>
+  </si>
+  <si>
+    <t>zh34</t>
+  </si>
+  <si>
+    <t>zh35</t>
+  </si>
+  <si>
+    <t>nan5</t>
+  </si>
+  <si>
+    <t>zh36</t>
+  </si>
+  <si>
+    <t>zh37</t>
+  </si>
+  <si>
+    <t>ja21</t>
+  </si>
+  <si>
+    <t>ja22</t>
+  </si>
+  <si>
+    <t>ja23</t>
+  </si>
+  <si>
+    <t>en5</t>
+  </si>
+  <si>
+    <t>zh38</t>
+  </si>
+  <si>
+    <t>zh39</t>
+  </si>
+  <si>
+    <t>zh40</t>
+  </si>
+  <si>
+    <t>zh41</t>
+  </si>
+  <si>
+    <t>nan6</t>
+  </si>
+  <si>
+    <t>hak1</t>
+  </si>
+  <si>
+    <t>yue1</t>
+  </si>
+  <si>
+    <t>nan7</t>
+  </si>
+  <si>
+    <t>zh42</t>
+  </si>
+  <si>
+    <t>zh43</t>
+  </si>
+  <si>
+    <t>zh44</t>
+  </si>
+  <si>
+    <t>zh45</t>
+  </si>
+  <si>
+    <t>zh46</t>
+  </si>
+  <si>
+    <t>zh47</t>
+  </si>
+  <si>
+    <t>zh48</t>
+  </si>
+  <si>
+    <t>zh49</t>
+  </si>
+  <si>
+    <t>zh50</t>
+  </si>
+  <si>
+    <t>zh51</t>
+  </si>
+  <si>
+    <t>zh52</t>
+  </si>
+  <si>
+    <t>ja24</t>
+  </si>
+  <si>
+    <t>zh53</t>
+  </si>
+  <si>
+    <t>ko1</t>
+  </si>
+  <si>
+    <t>zh54</t>
+  </si>
+  <si>
+    <t>zh55</t>
+  </si>
+  <si>
+    <t>zh56</t>
+  </si>
+  <si>
+    <t>ko2</t>
+  </si>
+  <si>
+    <t>zh57</t>
+  </si>
+  <si>
+    <t>ja25</t>
+  </si>
+  <si>
+    <t>ja26</t>
+  </si>
+  <si>
+    <t>zh58</t>
+  </si>
+  <si>
+    <t>ja27</t>
+  </si>
+  <si>
+    <t>ja28</t>
+  </si>
+  <si>
+    <t>ja29</t>
+  </si>
+  <si>
+    <t>ja30</t>
+  </si>
+  <si>
+    <t>ja31</t>
+  </si>
+  <si>
+    <t>ja32</t>
+  </si>
+  <si>
+    <t>一支小雨傘</t>
+  </si>
+  <si>
+    <t>洪榮宏</t>
+  </si>
+  <si>
+    <t>下一個天亮</t>
+  </si>
+  <si>
+    <t>郭靜</t>
+  </si>
+  <si>
     <t>大笑之歌</t>
   </si>
   <si>
-    <t>Cover</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
+    <t>四千金</t>
+  </si>
+  <si>
+    <t>大番薯</t>
+  </si>
+  <si>
+    <t>童謠</t>
+  </si>
+  <si>
+    <t>小幸運</t>
+  </si>
+  <si>
+    <t>田馥甄</t>
+  </si>
+  <si>
+    <t>不可幸力</t>
+  </si>
+  <si>
+    <t>Vaundy</t>
+  </si>
+  <si>
+    <t>不夠成熟</t>
+  </si>
+  <si>
+    <t>BY2</t>
+  </si>
+  <si>
+    <t>分手後不要做朋友</t>
+  </si>
+  <si>
+    <t>梁文音</t>
+  </si>
+  <si>
+    <t>天黑黑</t>
+  </si>
+  <si>
+    <t>孫燕姿</t>
+  </si>
+  <si>
+    <t>太陽與地球</t>
+  </si>
+  <si>
+    <t>盧廣仲</t>
+  </si>
+  <si>
+    <t>黃瑋中</t>
+  </si>
+  <si>
+    <t>水星記</t>
+  </si>
+  <si>
+    <t>郭頂</t>
+  </si>
+  <si>
+    <t>半句再見</t>
+  </si>
+  <si>
+    <t>白日</t>
+  </si>
+  <si>
+    <t>King Gnu</t>
+  </si>
+  <si>
+    <t>再會啦心愛的無緣的人</t>
+  </si>
+  <si>
+    <t>施文彬</t>
+  </si>
+  <si>
+    <t>因為單身的緣故</t>
+  </si>
+  <si>
+    <t>李宗盛</t>
+  </si>
+  <si>
+    <t>在迦納共和國離婚</t>
+  </si>
+  <si>
+    <t>菲道爾 &amp; 大穎</t>
+  </si>
+  <si>
+    <t>她說</t>
+  </si>
+  <si>
+    <t>林俊傑</t>
+  </si>
+  <si>
+    <t>如果我不知道</t>
+  </si>
+  <si>
+    <t>張語噥</t>
+  </si>
+  <si>
+    <t>年輪說</t>
+  </si>
+  <si>
+    <t>楊丞琳</t>
+  </si>
+  <si>
+    <t>有一種悲傷</t>
+  </si>
+  <si>
+    <t>A-Lin</t>
+  </si>
+  <si>
+    <t>老鼠愛大米</t>
+  </si>
+  <si>
+    <t>王啟文</t>
+  </si>
+  <si>
+    <t>自導自演</t>
+  </si>
+  <si>
+    <t>慢慢說</t>
+  </si>
+  <si>
+    <t>你就不要想起我</t>
+  </si>
+  <si>
+    <t>別の人の彼女になったよ</t>
+  </si>
+  <si>
+    <t>wacci</t>
+  </si>
+  <si>
+    <t>含淚跳恰恰</t>
+  </si>
+  <si>
+    <t>謝金燕</t>
+  </si>
+  <si>
+    <t>我不配</t>
+  </si>
+  <si>
+    <t>周杰倫</t>
+  </si>
+  <si>
+    <t>我不難過</t>
+  </si>
+  <si>
+    <t>我在紐約打電話給你</t>
+  </si>
+  <si>
+    <t>魏如萱</t>
+  </si>
+  <si>
+    <t>我的歌聲裡</t>
+  </si>
+  <si>
+    <t>曲婉婷</t>
+  </si>
+  <si>
+    <t>我是恁老爸</t>
+  </si>
+  <si>
+    <t>猪哥亮</t>
+  </si>
+  <si>
+    <t>我們不一樣</t>
+  </si>
+  <si>
+    <t>大壯</t>
+  </si>
+  <si>
+    <t>我想我不會愛你</t>
+  </si>
+  <si>
+    <t>我想要佔據你</t>
+  </si>
+  <si>
+    <t>告五人</t>
+  </si>
+  <si>
+    <t>我會好好的</t>
+  </si>
+  <si>
+    <t>王心凌</t>
+  </si>
+  <si>
+    <t>我懷念的</t>
+  </si>
+  <si>
+    <t>刻在我心底的名字</t>
+  </si>
+  <si>
+    <t>孤獨的總和</t>
+  </si>
+  <si>
+    <t>吳汶芳</t>
+  </si>
+  <si>
+    <t>怪獣の花唄</t>
+  </si>
+  <si>
+    <t>明明就</t>
+  </si>
+  <si>
+    <t>東京フラッシュ</t>
+  </si>
+  <si>
+    <t>知道</t>
+  </si>
+  <si>
+    <t>雨愛</t>
+  </si>
+  <si>
+    <t>変わらないもの</t>
+  </si>
+  <si>
+    <t>奥華子 / 跳躍吧！時空少女</t>
+  </si>
+  <si>
+    <t>革命道中</t>
+  </si>
+  <si>
+    <t>アイナ・ジ・エンド</t>
+  </si>
+  <si>
+    <t>香水</t>
+  </si>
+  <si>
+    <t>瑛人</t>
+  </si>
+  <si>
+    <t>江志豐 vs 張秀卿</t>
+  </si>
+  <si>
+    <t>修練愛情</t>
+  </si>
+  <si>
+    <t>倒帶</t>
+  </si>
+  <si>
+    <t>蔡依林</t>
+  </si>
+  <si>
+    <t>挪威的森林</t>
+  </si>
+  <si>
+    <t>伍佰</t>
+  </si>
+  <si>
+    <t>浪子回頭</t>
+  </si>
+  <si>
+    <t>茄子蛋</t>
+  </si>
+  <si>
+    <t>逆光</t>
+  </si>
+  <si>
+    <t>逆さまの蝶</t>
+  </si>
+  <si>
+    <t>SNoW / 地獄少女OP</t>
+  </si>
+  <si>
+    <t>鬼ノ宴(Demons Banquet)</t>
+  </si>
+  <si>
+    <t>友成空</t>
+  </si>
+  <si>
+    <t>偽顏</t>
+  </si>
+  <si>
+    <t>yama</t>
+  </si>
+  <si>
+    <t>寂寞寂寞就好</t>
+  </si>
+  <si>
+    <t>帶我走</t>
+  </si>
+  <si>
+    <t>捲菸</t>
+  </si>
+  <si>
+    <t>美秀集團</t>
+  </si>
+  <si>
+    <t>逢いたくていま</t>
+  </si>
+  <si>
+    <t>MISIA</t>
+  </si>
+  <si>
+    <t>喜劇收場</t>
+  </si>
+  <si>
+    <t>幾分之幾</t>
+  </si>
+  <si>
+    <t>盧廣仲 / 花甲大人轉男孩</t>
+  </si>
+  <si>
+    <t>渺小</t>
+  </si>
+  <si>
+    <t>買你</t>
+  </si>
+  <si>
+    <t>開始懂了</t>
+  </si>
+  <si>
+    <t>微加幸福</t>
+  </si>
+  <si>
+    <t>郁可唯</t>
+  </si>
+  <si>
+    <t>愛情怎麼了嗎</t>
+  </si>
+  <si>
+    <t>愛過的樣子</t>
+  </si>
+  <si>
+    <t>王艷薇</t>
+  </si>
+  <si>
+    <t>舅媽</t>
+  </si>
+  <si>
+    <t>巴大雄</t>
+  </si>
+  <si>
+    <t>落雨聲</t>
+  </si>
+  <si>
+    <t>江蕙</t>
+  </si>
+  <si>
+    <t>路過人間</t>
+  </si>
+  <si>
+    <t>遇見</t>
+  </si>
+  <si>
+    <t>像天堂的懸崖</t>
+  </si>
+  <si>
+    <t>李佳薇</t>
+  </si>
+  <si>
+    <t>夢醒時分</t>
+  </si>
+  <si>
+    <t>慢冷</t>
+  </si>
+  <si>
+    <t>梁靜茹</t>
+  </si>
+  <si>
+    <t>踊り子</t>
+  </si>
+  <si>
+    <t>曖昧</t>
+  </si>
+  <si>
+    <t>藍</t>
+  </si>
+  <si>
+    <t>石白其</t>
+  </si>
+  <si>
+    <t>聽見下雨的聲音</t>
+  </si>
+  <si>
+    <t>魏如昀</t>
+  </si>
+  <si>
+    <t>體面</t>
+  </si>
+  <si>
+    <t>于文文</t>
+  </si>
+  <si>
+    <t>ACT/アクト</t>
+  </si>
+  <si>
+    <t>Giga, TeddyLoid, Daoko</t>
   </si>
   <si>
     <t>BAD GUY</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
-  </si>
-  <si>
-    <t>ACT/アクト</t>
-  </si>
-  <si>
-    <t>7:16</t>
-  </si>
-  <si>
-    <t>藍</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>17:34</t>
-  </si>
-  <si>
-    <t>路過人間</t>
-  </si>
-  <si>
-    <t>21:56</t>
-  </si>
-  <si>
-    <t>半句再見</t>
-  </si>
-  <si>
-    <t>26:23</t>
-  </si>
-  <si>
-    <t>慢冷</t>
-  </si>
-  <si>
-    <t>32:29</t>
+    <t>Billie Eilish</t>
+  </si>
+  <si>
+    <t>Breathe</t>
+  </si>
+  <si>
+    <t>Lee Hi</t>
+  </si>
+  <si>
+    <t>Bunny Girl</t>
+  </si>
+  <si>
+    <t>AKASAKI</t>
+  </si>
+  <si>
+    <t>Bのリベンジ</t>
+  </si>
+  <si>
+    <t>B小町 ルビー(伊駒ゆりえ)、有馬かな(潘めぐみ)、MEMちょ(大久保瑠美)</t>
+  </si>
+  <si>
+    <t>CoCo</t>
+  </si>
+  <si>
+    <t>O.T. Genasis</t>
+  </si>
+  <si>
+    <t>Hero's Come Back!!</t>
+  </si>
+  <si>
+    <t>nobodyknows+ / 火影忍者疾風傳OP</t>
+  </si>
+  <si>
+    <t>i love you</t>
+  </si>
+  <si>
+    <t>IRIS OUT</t>
+  </si>
+  <si>
+    <t>米津玄師</t>
   </si>
   <si>
     <t>JANE DOE</t>
   </si>
   <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>33:52</t>
-  </si>
-  <si>
-    <t>34:58</t>
-  </si>
-  <si>
-    <t>37:38</t>
-  </si>
-  <si>
-    <t>40:59</t>
-  </si>
-  <si>
-    <t>IRIS OUT</t>
-  </si>
-  <si>
-    <t>42:09</t>
-  </si>
-  <si>
-    <t>44:43</t>
-  </si>
-  <si>
-    <t>革命道中</t>
-  </si>
-  <si>
-    <t>47:01</t>
-  </si>
-  <si>
-    <t>含淚跳恰恰</t>
-  </si>
-  <si>
-    <t>52:08</t>
-  </si>
-  <si>
-    <t>孤獨的總和</t>
-  </si>
-  <si>
-    <t>57:34</t>
-  </si>
-  <si>
-    <t>挪威的森林</t>
-  </si>
-  <si>
-    <t>觀眾唱</t>
-  </si>
-  <si>
-    <t>1:03:45</t>
-  </si>
-  <si>
-    <t>買你</t>
-  </si>
-  <si>
-    <t>1:08:09</t>
-  </si>
-  <si>
-    <t>我在紐約打電話給你</t>
-  </si>
-  <si>
-    <t>1:12:27</t>
-  </si>
-  <si>
-    <t>開始懂了</t>
-  </si>
-  <si>
-    <t>1:17:44</t>
-  </si>
-  <si>
-    <t>我不難過</t>
-  </si>
-  <si>
-    <t>切歌</t>
-  </si>
-  <si>
-    <t>1:18:47</t>
-  </si>
-  <si>
-    <t>1:25:12</t>
-  </si>
-  <si>
-    <t>我懷念的</t>
-  </si>
-  <si>
-    <t>1:33:37</t>
-  </si>
-  <si>
-    <t>再會啦心愛的無緣的人</t>
-  </si>
-  <si>
-    <t>4:15:50</t>
-  </si>
-  <si>
-    <t>我們不一樣</t>
-  </si>
-  <si>
-    <t>4:18:46</t>
-  </si>
-  <si>
-    <t>因為單身的緣故</t>
-  </si>
-  <si>
-    <t>4:20:12</t>
-  </si>
-  <si>
-    <t>​​Bunny Girl</t>
-  </si>
-  <si>
-    <t>4:24:52</t>
+    <t>米津玄師, 宇多田ヒカル</t>
+  </si>
+  <si>
+    <t>Miniskirt</t>
+  </si>
+  <si>
+    <t>AOA</t>
+  </si>
+  <si>
+    <t>NIGHT DANCER</t>
+  </si>
+  <si>
+    <t>imase</t>
+  </si>
+  <si>
+    <t>Overdose</t>
+  </si>
+  <si>
+    <t>なとり</t>
+  </si>
+  <si>
+    <t>Playground</t>
+  </si>
+  <si>
+    <t>Bea Miller</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>壞特</t>
+  </si>
+  <si>
+    <t>the WORLD</t>
+  </si>
+  <si>
+    <t>NIGHTMARE / 死亡筆記本OP</t>
+  </si>
+  <si>
+    <t>wish you were gay</t>
+  </si>
+  <si>
+    <t>いのちの名前</t>
+  </si>
+  <si>
+    <t>木村弓 / 神隱少女</t>
+  </si>
+  <si>
+    <t>カタオモイ</t>
+  </si>
+  <si>
+    <t>Aimer</t>
+  </si>
+  <si>
+    <t>シンデレラボーイ</t>
+  </si>
+  <si>
+    <t>石原慎也</t>
+  </si>
+  <si>
+    <t>たばこ</t>
+  </si>
+  <si>
+    <t>ダズビー</t>
+  </si>
+  <si>
+    <t>どうせ無くなるだけ</t>
+  </si>
+  <si>
+    <t>たかやん</t>
+  </si>
+  <si>
+    <t>ドライフラワー</t>
+  </si>
+  <si>
+    <t>優里</t>
+  </si>
+  <si>
+    <t>なんか幸せ</t>
+  </si>
+  <si>
+    <t>烈火之炎OP</t>
   </si>
   <si>
     <t>プロポーズ</t>
   </si>
   <si>
-    <t>4:27:12</t>
-  </si>
-  <si>
-    <t>鬼ノ宴(Demons Banquet)</t>
-  </si>
-  <si>
-    <t>4:29:40</t>
+    <t>ホウキ雲</t>
+  </si>
+  <si>
+    <t>RYTHEM / 烘焙王OP</t>
   </si>
   <si>
     <t>ほろよい</t>
-  </si>
-  <si>
-    <t>4:32:59</t>
-  </si>
-  <si>
-    <t>Overdose</t>
-  </si>
-  <si>
-    <t>4:35:26</t>
-  </si>
-  <si>
-    <t>東京フラッシュ</t>
-  </si>
-  <si>
-    <t>4:38:47</t>
-  </si>
-  <si>
-    <t>踊り子</t>
-  </si>
-  <si>
-    <t>4:44:17</t>
-  </si>
-  <si>
-    <t>wish you were gay</t>
-  </si>
-  <si>
-    <t>4:48:35</t>
-  </si>
-  <si>
-    <t>i love you</t>
-  </si>
-  <si>
-    <t>4:53:54</t>
-  </si>
-  <si>
-    <t>4:59:15</t>
-  </si>
-  <si>
-    <t>微加幸福</t>
-  </si>
-  <si>
-    <t>5:04:18</t>
-  </si>
-  <si>
-    <t>CoCo</t>
-  </si>
-  <si>
-    <t>5:10:38</t>
-  </si>
-  <si>
-    <t>5:14:05</t>
-  </si>
-  <si>
-    <t>5:15:38</t>
-  </si>
-  <si>
-    <t>5:20:33</t>
-  </si>
-  <si>
-    <t>偽顏</t>
-  </si>
-  <si>
-    <t>5:21:48</t>
-  </si>
-  <si>
-    <t>5:26:07</t>
-  </si>
-  <si>
-    <t>カタオモイ</t>
-  </si>
-  <si>
-    <t>5:28:28</t>
-  </si>
-  <si>
-    <t>NIGHT DANCER</t>
-  </si>
-  <si>
-    <t>5:35:39</t>
-  </si>
-  <si>
-    <t>どうせ無くなるだけ</t>
-  </si>
-  <si>
-    <t>5:41:14</t>
-  </si>
-  <si>
-    <t>怪獣の花唄</t>
-  </si>
-  <si>
-    <t>5:43:10</t>
-  </si>
-  <si>
-    <t>ドライフラワー</t>
-  </si>
-  <si>
-    <t>5:47:00</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>5:49:00</t>
-  </si>
-  <si>
-    <t>5:52:55</t>
-  </si>
-  <si>
-    <t>不可幸力</t>
-  </si>
-  <si>
-    <t>5:56:05</t>
-  </si>
-  <si>
-    <t>逆さまの蝶</t>
-  </si>
-  <si>
-    <t>5:58:06</t>
-  </si>
-  <si>
-    <t>體面</t>
-  </si>
-  <si>
-    <t>6:01:13</t>
-  </si>
-  <si>
-    <t>香水</t>
-  </si>
-  <si>
-    <t>6:03:12</t>
-  </si>
-  <si>
-    <t>6:05:24</t>
-  </si>
-  <si>
-    <t>捲菸</t>
-  </si>
-  <si>
-    <t>6:09:58</t>
-  </si>
-  <si>
-    <t>浪子回頭</t>
-  </si>
-  <si>
-    <t>6:11:14</t>
-  </si>
-  <si>
-    <t>6:13:40</t>
-  </si>
-  <si>
-    <t>6:18:16</t>
-  </si>
-  <si>
-    <t>6:24:26</t>
-  </si>
-  <si>
-    <t>刻在我心底的名字</t>
-  </si>
-  <si>
-    <t>6:36:21</t>
-  </si>
-  <si>
-    <t>幾分之幾</t>
-  </si>
-  <si>
-    <t>6:46:04</t>
-  </si>
-  <si>
-    <t>明明就</t>
-  </si>
-  <si>
-    <t>6:53:33</t>
-  </si>
-  <si>
-    <t>7:03:34</t>
-  </si>
-  <si>
-    <t>7:08:22</t>
-  </si>
-  <si>
-    <t>39:47</t>
-  </si>
-  <si>
-    <t>寂寞寂寞就好</t>
-  </si>
-  <si>
-    <t>45:02</t>
-  </si>
-  <si>
-    <t>51:24</t>
-  </si>
-  <si>
-    <t>倒帶</t>
-  </si>
-  <si>
-    <t>56:42</t>
-  </si>
-  <si>
-    <t>1:02:53</t>
-  </si>
-  <si>
-    <t>1:14:02</t>
-  </si>
-  <si>
-    <t>知道</t>
-  </si>
-  <si>
-    <t>1:19:07</t>
-  </si>
-  <si>
-    <t>曖昧</t>
-  </si>
-  <si>
-    <t>1:26:53</t>
-  </si>
-  <si>
-    <t>小幸運</t>
-  </si>
-  <si>
-    <t>1:33:50</t>
-  </si>
-  <si>
-    <t>喜劇收場</t>
-  </si>
-  <si>
-    <t>1:40:01</t>
-  </si>
-  <si>
-    <t>不夠成熟</t>
-  </si>
-  <si>
-    <t>1:47:22</t>
-  </si>
-  <si>
-    <t>分手後不要做朋友</t>
-  </si>
-  <si>
-    <t>1:59:55</t>
-  </si>
-  <si>
-    <t>我不配</t>
-  </si>
-  <si>
-    <t>2:05:01</t>
-  </si>
-  <si>
-    <t>2:14:03</t>
-  </si>
-  <si>
-    <t>老鼠愛大米</t>
-  </si>
-  <si>
-    <t>2:16:55</t>
-  </si>
-  <si>
-    <t>下一個天亮</t>
-  </si>
-  <si>
-    <t>2:22:12</t>
-  </si>
-  <si>
-    <t>像天堂的懸崖</t>
-  </si>
-  <si>
-    <t>2:27:49</t>
-  </si>
-  <si>
-    <t>有一種悲傷</t>
-  </si>
-  <si>
-    <t>2:35:24</t>
-  </si>
-  <si>
-    <t>聽見下雨的聲音</t>
-  </si>
-  <si>
-    <t>2:40:30</t>
-  </si>
-  <si>
-    <t>落雨聲</t>
-  </si>
-  <si>
-    <t>2:50:00</t>
-  </si>
-  <si>
-    <t>你就不要想起我</t>
-  </si>
-  <si>
-    <t>2:54:45</t>
-  </si>
-  <si>
-    <t>3:00:18</t>
-  </si>
-  <si>
-    <t>3:11:22</t>
-  </si>
-  <si>
-    <t>3:22:00</t>
-  </si>
-  <si>
-    <t>雨愛</t>
-  </si>
-  <si>
-    <t>3:29:16</t>
-  </si>
-  <si>
-    <t>白日</t>
-  </si>
-  <si>
-    <t>3:30:42</t>
-  </si>
-  <si>
-    <t>逢いたくていま</t>
-  </si>
-  <si>
-    <t>3:39:48</t>
-  </si>
-  <si>
-    <t>ホウキ雲</t>
-  </si>
-  <si>
-    <t>3:43:29</t>
-  </si>
-  <si>
-    <t>3:48:22</t>
-  </si>
-  <si>
-    <t>3:53:31</t>
-  </si>
-  <si>
-    <t>3:55:11</t>
-  </si>
-  <si>
-    <t>Bunny Girl</t>
-  </si>
-  <si>
-    <t>4:01:19</t>
-  </si>
-  <si>
-    <t>4:06:47</t>
-  </si>
-  <si>
-    <t>Playground</t>
-  </si>
-  <si>
-    <t>4:09:57</t>
-  </si>
-  <si>
-    <t>渺小</t>
-  </si>
-  <si>
-    <t>4:16:28</t>
-  </si>
-  <si>
-    <t>我想我不會愛你</t>
-  </si>
-  <si>
-    <t>4:19:07</t>
-  </si>
-  <si>
-    <t>年輪說</t>
-  </si>
-  <si>
-    <t>4:23:01</t>
-  </si>
-  <si>
-    <t>夢醒時分</t>
-  </si>
-  <si>
-    <t>4:27:49</t>
-  </si>
-  <si>
-    <t>我是恁老爸</t>
-  </si>
-  <si>
-    <t>1:31:53</t>
-  </si>
-  <si>
-    <t>大番薯</t>
-  </si>
-  <si>
-    <t>3:27:05</t>
-  </si>
-  <si>
-    <t>太陽與地球</t>
-  </si>
-  <si>
-    <t>3:28:00</t>
-  </si>
-  <si>
-    <t>4:20:39</t>
-  </si>
-  <si>
-    <t>一支小雨傘</t>
-  </si>
-  <si>
-    <t>8:47</t>
-  </si>
-  <si>
-    <t>愛過的樣子</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>14:27</t>
-  </si>
-  <si>
-    <t>25:09</t>
-  </si>
-  <si>
-    <t>如果我不知道</t>
-  </si>
-  <si>
-    <t>25:49</t>
-  </si>
-  <si>
-    <t>29:05</t>
-  </si>
-  <si>
-    <t>在迦納共和國離婚</t>
-  </si>
-  <si>
-    <t>33:29</t>
-  </si>
-  <si>
-    <t>40:42</t>
-  </si>
-  <si>
-    <t>自導自演</t>
-  </si>
-  <si>
-    <t>45:40</t>
-  </si>
-  <si>
-    <t>47:26</t>
-  </si>
-  <si>
-    <t>50:58</t>
-  </si>
-  <si>
-    <t>52:33</t>
-  </si>
-  <si>
-    <t>改編</t>
-  </si>
-  <si>
-    <t>55:15</t>
-  </si>
-  <si>
-    <t>水星記</t>
-  </si>
-  <si>
-    <t>1:00:20</t>
-  </si>
-  <si>
-    <t>1:06:09</t>
-  </si>
-  <si>
-    <t>愛情怎麼了嗎</t>
-  </si>
-  <si>
-    <t>1:10:44</t>
-  </si>
-  <si>
-    <t>1:16:37</t>
-  </si>
-  <si>
-    <t>我的歌聲裡</t>
-  </si>
-  <si>
-    <t>1:21:35</t>
-  </si>
-  <si>
-    <t>舅媽</t>
-  </si>
-  <si>
-    <t>1:26:58</t>
-  </si>
-  <si>
-    <t>帶我走</t>
-  </si>
-  <si>
-    <t>1:31:34</t>
-  </si>
-  <si>
-    <t>片段</t>
-  </si>
-  <si>
-    <t>1:36:36</t>
-  </si>
-  <si>
-    <t>1:37:35</t>
-  </si>
-  <si>
-    <t>1:43:06</t>
-  </si>
-  <si>
-    <t>1:47:01</t>
-  </si>
-  <si>
-    <t>她說</t>
-  </si>
-  <si>
-    <t>1:54:59</t>
-  </si>
-  <si>
-    <t>別の人の彼女になったよ</t>
-  </si>
-  <si>
-    <t>開夾</t>
-  </si>
-  <si>
-    <t>2:03:06</t>
-  </si>
-  <si>
-    <t>2:07:16</t>
-  </si>
-  <si>
-    <t>2:11:07</t>
-  </si>
-  <si>
-    <t>2:11:50</t>
-  </si>
-  <si>
-    <t>27:28</t>
-  </si>
-  <si>
-    <t>我會好好的</t>
-  </si>
-  <si>
-    <t>32:40</t>
-  </si>
-  <si>
-    <t>Breathe</t>
-  </si>
-  <si>
-    <t>34:45</t>
-  </si>
-  <si>
-    <t>37:49</t>
-  </si>
-  <si>
-    <t>天黑黑</t>
-  </si>
-  <si>
-    <t>42:49</t>
-  </si>
-  <si>
-    <t>遇見</t>
-  </si>
-  <si>
-    <t>47:34</t>
-  </si>
-  <si>
-    <t>53:10</t>
-  </si>
-  <si>
-    <t>我想要佔據你</t>
-  </si>
-  <si>
-    <t>1:01:05</t>
-  </si>
-  <si>
-    <t>Miniskirt</t>
-  </si>
-  <si>
-    <t>1:04:58</t>
-  </si>
-  <si>
-    <t>修練愛情</t>
-  </si>
-  <si>
-    <t>1:09:59</t>
-  </si>
-  <si>
-    <t>なんか幸せ</t>
-  </si>
-  <si>
-    <t>1:17:22</t>
-  </si>
-  <si>
-    <t>変わらないもの</t>
-  </si>
-  <si>
-    <t>2:48:50</t>
-  </si>
-  <si>
-    <t>逆光</t>
-  </si>
-  <si>
-    <t>3:02:49</t>
-  </si>
-  <si>
-    <t>3:06:56</t>
-  </si>
-  <si>
-    <t>3:18:02</t>
-  </si>
-  <si>
-    <t>いのちの名前</t>
-  </si>
-  <si>
-    <t>3:22:40</t>
-  </si>
-  <si>
-    <t>シンデレラボーイ</t>
-  </si>
-  <si>
-    <t>3:28:24</t>
-  </si>
-  <si>
-    <t>たばこ</t>
-  </si>
-  <si>
-    <t>3:35:00</t>
-  </si>
-  <si>
-    <t>Hero's Come Back!!</t>
-  </si>
-  <si>
-    <t>3:41:11</t>
-  </si>
-  <si>
-    <t>the WORLD</t>
-  </si>
-  <si>
-    <t>3:42:35</t>
-  </si>
-  <si>
-    <t>https://youtu.be/bZn2uiXpNvE?t=13311</t>
-  </si>
-  <si>
-    <t>知花</t>
-  </si>
-  <si>
-    <t>合唱</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=G_5bOFykGPs</t>
-  </si>
-  <si>
-    <t>Bのリベンジ</t>
-  </si>
-  <si>
-    <t>福栗, 真理果</t>
-  </si>
-  <si>
-    <t>Cover, 合唱</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=zbOsJbnkhyk</t>
-  </si>
-  <si>
-    <t>神崎アルファ</t>
-  </si>
-  <si>
-    <t>zh1</t>
-  </si>
-  <si>
-    <t>en1</t>
-  </si>
-  <si>
-    <t>ja1</t>
-  </si>
-  <si>
-    <t>zh2</t>
-  </si>
-  <si>
-    <t>zh3</t>
-  </si>
-  <si>
-    <t>zh4</t>
-  </si>
-  <si>
-    <t>zh5</t>
-  </si>
-  <si>
-    <t>ja2</t>
-  </si>
-  <si>
-    <t>ja3</t>
-  </si>
-  <si>
-    <t>ja4</t>
-  </si>
-  <si>
-    <t>nan1</t>
-  </si>
-  <si>
-    <t>zh6</t>
-  </si>
-  <si>
-    <t>zh7</t>
-  </si>
-  <si>
-    <t>zh8</t>
-  </si>
-  <si>
-    <t>zh9</t>
-  </si>
-  <si>
-    <t>zh10</t>
-  </si>
-  <si>
-    <t>zh11</t>
-  </si>
-  <si>
-    <t>zh12</t>
-  </si>
-  <si>
-    <t>nan2</t>
-  </si>
-  <si>
-    <t>zh13</t>
-  </si>
-  <si>
-    <t>zh14</t>
-  </si>
-  <si>
-    <t>ja5</t>
-  </si>
-  <si>
-    <t>ja6</t>
-  </si>
-  <si>
-    <t>ja7</t>
-  </si>
-  <si>
-    <t>ja8</t>
-  </si>
-  <si>
-    <t>ja9</t>
-  </si>
-  <si>
-    <t>ja10</t>
-  </si>
-  <si>
-    <t>ja11</t>
-  </si>
-  <si>
-    <t>en2</t>
-  </si>
-  <si>
-    <t>en3</t>
-  </si>
-  <si>
-    <t>zh15</t>
-  </si>
-  <si>
-    <t>en4</t>
-  </si>
-  <si>
-    <t>ja12</t>
-  </si>
-  <si>
-    <t>ja13</t>
-  </si>
-  <si>
-    <t>ja14</t>
-  </si>
-  <si>
-    <t>ja15</t>
-  </si>
-  <si>
-    <t>ja16</t>
-  </si>
-  <si>
-    <t>ja17</t>
-  </si>
-  <si>
-    <t>zh16</t>
-  </si>
-  <si>
-    <t>ja18</t>
-  </si>
-  <si>
-    <t>ja19</t>
-  </si>
-  <si>
-    <t>zh17</t>
-  </si>
-  <si>
-    <t>ja20</t>
-  </si>
-  <si>
-    <t>zh18</t>
-  </si>
-  <si>
-    <t>nan4</t>
-  </si>
-  <si>
-    <t>zh19</t>
-  </si>
-  <si>
-    <t>zh20</t>
-  </si>
-  <si>
-    <t>zh21</t>
-  </si>
-  <si>
-    <t>zh22</t>
-  </si>
-  <si>
-    <t>zh23</t>
-  </si>
-  <si>
-    <t>zh24</t>
-  </si>
-  <si>
-    <t>zh25</t>
-  </si>
-  <si>
-    <t>zh26</t>
-  </si>
-  <si>
-    <t>zh27</t>
-  </si>
-  <si>
-    <t>zh28</t>
-  </si>
-  <si>
-    <t>zh29</t>
-  </si>
-  <si>
-    <t>zh30</t>
-  </si>
-  <si>
-    <t>zh31</t>
-  </si>
-  <si>
-    <t>zh32</t>
-  </si>
-  <si>
-    <t>zh33</t>
-  </si>
-  <si>
-    <t>zh34</t>
-  </si>
-  <si>
-    <t>zh35</t>
-  </si>
-  <si>
-    <t>nan5</t>
-  </si>
-  <si>
-    <t>zh36</t>
-  </si>
-  <si>
-    <t>zh37</t>
-  </si>
-  <si>
-    <t>ja21</t>
-  </si>
-  <si>
-    <t>ja22</t>
-  </si>
-  <si>
-    <t>ja23</t>
-  </si>
-  <si>
-    <t>en5</t>
-  </si>
-  <si>
-    <t>zh38</t>
-  </si>
-  <si>
-    <t>zh39</t>
-  </si>
-  <si>
-    <t>zh40</t>
-  </si>
-  <si>
-    <t>zh41</t>
-  </si>
-  <si>
-    <t>nan6</t>
-  </si>
-  <si>
-    <t>hak1</t>
-  </si>
-  <si>
-    <t>zh46</t>
-  </si>
-  <si>
-    <t>nan7</t>
-  </si>
-  <si>
-    <t>zh42</t>
-  </si>
-  <si>
-    <t>zh43</t>
-  </si>
-  <si>
-    <t>zh44</t>
-  </si>
-  <si>
-    <t>zh45</t>
-  </si>
-  <si>
-    <t>zh47</t>
-  </si>
-  <si>
-    <t>zh48</t>
-  </si>
-  <si>
-    <t>zh49</t>
-  </si>
-  <si>
-    <t>zh50</t>
-  </si>
-  <si>
-    <t>zh51</t>
-  </si>
-  <si>
-    <t>zh52</t>
-  </si>
-  <si>
-    <t>ja24</t>
-  </si>
-  <si>
-    <t>zh53</t>
-  </si>
-  <si>
-    <t>ko1</t>
-  </si>
-  <si>
-    <t>zh54</t>
-  </si>
-  <si>
-    <t>zh55</t>
-  </si>
-  <si>
-    <t>zh56</t>
-  </si>
-  <si>
-    <t>ko2</t>
-  </si>
-  <si>
-    <t>zh57</t>
-  </si>
-  <si>
-    <t>ja25</t>
-  </si>
-  <si>
-    <t>ja26</t>
-  </si>
-  <si>
-    <t>zh58</t>
-  </si>
-  <si>
-    <t>ja27</t>
-  </si>
-  <si>
-    <t>ja28</t>
-  </si>
-  <si>
-    <t>ja29</t>
-  </si>
-  <si>
-    <t>ja30</t>
-  </si>
-  <si>
-    <t>ja31</t>
-  </si>
-  <si>
-    <t>ja32</t>
-  </si>
-  <si>
-    <t>洪榮宏</t>
-  </si>
-  <si>
-    <t>郭靜</t>
-  </si>
-  <si>
-    <t>四千金</t>
-  </si>
-  <si>
-    <t>童謠</t>
-  </si>
-  <si>
-    <t>田馥甄</t>
-  </si>
-  <si>
-    <t>Vaundy</t>
-  </si>
-  <si>
-    <t>BY2</t>
-  </si>
-  <si>
-    <t>梁文音</t>
-  </si>
-  <si>
-    <t>孫燕姿</t>
-  </si>
-  <si>
-    <t>盧廣仲</t>
-  </si>
-  <si>
-    <t>yue1</t>
-  </si>
-  <si>
-    <t>黃瑋中</t>
-  </si>
-  <si>
-    <t>郭頂</t>
-  </si>
-  <si>
-    <t>King Gnu</t>
-  </si>
-  <si>
-    <t>施文彬</t>
-  </si>
-  <si>
-    <t>李宗盛</t>
-  </si>
-  <si>
-    <t>菲道爾 &amp; 大穎</t>
-  </si>
-  <si>
-    <t>林俊傑</t>
-  </si>
-  <si>
-    <t>張語噥</t>
-  </si>
-  <si>
-    <t>楊丞琳</t>
-  </si>
-  <si>
-    <t>A-Lin</t>
-  </si>
-  <si>
-    <t>王啟文</t>
-  </si>
-  <si>
-    <t>慢慢說</t>
-  </si>
-  <si>
-    <t>wacci</t>
-  </si>
-  <si>
-    <t>謝金燕</t>
-  </si>
-  <si>
-    <t>周杰倫</t>
-  </si>
-  <si>
-    <t>魏如萱</t>
-  </si>
-  <si>
-    <t>曲婉婷</t>
-  </si>
-  <si>
-    <t>猪哥亮</t>
-  </si>
-  <si>
-    <t>大壯</t>
-  </si>
-  <si>
-    <t>告五人</t>
-  </si>
-  <si>
-    <t>王心凌</t>
-  </si>
-  <si>
-    <t>吳汶芳</t>
-  </si>
-  <si>
-    <t>奥華子 / 跳躍吧！時空少女</t>
-  </si>
-  <si>
-    <t>アイナ・ジ・エンド</t>
-  </si>
-  <si>
-    <t>瑛人</t>
-  </si>
-  <si>
-    <t>nan3</t>
-  </si>
-  <si>
-    <t>江志豐 vs 張秀卿</t>
-  </si>
-  <si>
-    <t>蔡依林</t>
-  </si>
-  <si>
-    <t>伍佰</t>
-  </si>
-  <si>
-    <t>茄子蛋</t>
-  </si>
-  <si>
-    <t>SNoW / 地獄少女OP</t>
-  </si>
-  <si>
-    <t>友成空</t>
-  </si>
-  <si>
-    <t>yama</t>
-  </si>
-  <si>
-    <t>美秀集團</t>
-  </si>
-  <si>
-    <t>MISIA</t>
-  </si>
-  <si>
-    <t>盧廣仲 / 花甲大人轉男孩</t>
-  </si>
-  <si>
-    <t>郁可唯</t>
-  </si>
-  <si>
-    <t>王艷薇</t>
-  </si>
-  <si>
-    <t>巴大雄</t>
-  </si>
-  <si>
-    <t>江蕙</t>
-  </si>
-  <si>
-    <t>李佳薇</t>
-  </si>
-  <si>
-    <t>梁靜茹</t>
-  </si>
-  <si>
-    <t>石白其</t>
-  </si>
-  <si>
-    <t>魏如昀</t>
-  </si>
-  <si>
-    <t>于文文</t>
-  </si>
-  <si>
-    <t>Giga, TeddyLoid, Daoko</t>
-  </si>
-  <si>
-    <t>Billie Eilish</t>
-  </si>
-  <si>
-    <t>Lee Hi</t>
-  </si>
-  <si>
-    <t>AKASAKI</t>
-  </si>
-  <si>
-    <t>B小町 ルビー(伊駒ゆりえ)、有馬かな(潘めぐみ)、MEMちょ(大久保瑠美)</t>
-  </si>
-  <si>
-    <t>O.T. Genasis</t>
-  </si>
-  <si>
-    <t>nobodyknows+ / 火影忍者疾風傳OP</t>
-  </si>
-  <si>
-    <t>米津玄師</t>
-  </si>
-  <si>
-    <t>米津玄師, 宇多田ヒカル</t>
-  </si>
-  <si>
-    <t>AOA</t>
-  </si>
-  <si>
-    <t>imase</t>
-  </si>
-  <si>
-    <t>なとり</t>
-  </si>
-  <si>
-    <t>Bea Miller</t>
-  </si>
-  <si>
-    <t>壞特</t>
-  </si>
-  <si>
-    <t>NIGHTMARE / 死亡筆記本OP</t>
-  </si>
-  <si>
-    <t>木村弓 / 神隱少女</t>
-  </si>
-  <si>
-    <t>Aimer</t>
-  </si>
-  <si>
-    <t>石原慎也</t>
-  </si>
-  <si>
-    <t>ダズビー</t>
-  </si>
-  <si>
-    <t>たかやん</t>
-  </si>
-  <si>
-    <t>優里</t>
-  </si>
-  <si>
-    <t>烈火之炎OP</t>
-  </si>
-  <si>
-    <t>RYTHEM / 烘焙王OP</t>
   </si>
   <si>
     <t>さんひ</t>
@@ -1752,13 +2070,13 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1766,17 +2084,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1784,17 +2102,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -1805,13 +2123,13 @@
         <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1822,13 +2140,13 @@
         <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1839,13 +2157,13 @@
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1856,13 +2174,13 @@
         <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1873,13 +2191,13 @@
         <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>121</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1890,16 +2208,16 @@
         <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1910,16 +2228,16 @@
         <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1930,16 +2248,16 @@
         <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1950,16 +2268,16 @@
         <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1970,16 +2288,16 @@
         <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1990,16 +2308,16 @@
         <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -2010,16 +2328,16 @@
         <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -2030,13 +2348,13 @@
         <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -2047,13 +2365,13 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -2064,16 +2382,16 @@
         <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2084,13 +2402,13 @@
         <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -2101,13 +2419,13 @@
         <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -2118,13 +2436,13 @@
         <v>24</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -2135,16 +2453,16 @@
         <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -2155,13 +2473,13 @@
         <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -2172,13 +2490,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -2189,13 +2507,13 @@
         <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -2206,16 +2524,16 @@
         <v>38</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -2226,16 +2544,16 @@
         <v>38</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -2246,13 +2564,13 @@
         <v>38</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -2263,16 +2581,16 @@
         <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -2283,16 +2601,16 @@
         <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -2303,16 +2621,16 @@
         <v>38</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -2323,16 +2641,16 @@
         <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -2343,16 +2661,16 @@
         <v>38</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -2363,13 +2681,13 @@
         <v>38</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -2380,13 +2698,13 @@
         <v>38</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -2397,13 +2715,13 @@
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -2414,13 +2732,13 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -2431,13 +2749,13 @@
         <v>38</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -2448,13 +2766,13 @@
         <v>38</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -2465,16 +2783,16 @@
         <v>38</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -2485,16 +2803,16 @@
         <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -2505,13 +2823,13 @@
         <v>38</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -2522,16 +2840,16 @@
         <v>38</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -2542,16 +2860,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -2562,16 +2880,16 @@
         <v>38</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -2582,13 +2900,13 @@
         <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -2599,13 +2917,13 @@
         <v>38</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -2616,16 +2934,16 @@
         <v>38</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -2636,16 +2954,16 @@
         <v>38</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -2656,16 +2974,16 @@
         <v>38</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -2676,13 +2994,13 @@
         <v>38</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -2693,16 +3011,16 @@
         <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>102</v>
+        <v>168</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2713,16 +3031,16 @@
         <v>38</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2733,16 +3051,16 @@
         <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2753,16 +3071,16 @@
         <v>38</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2773,16 +3091,16 @@
         <v>38</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>110</v>
+        <v>172</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2793,13 +3111,13 @@
         <v>38</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2810,16 +3128,16 @@
         <v>38</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2830,16 +3148,16 @@
         <v>38</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2850,13 +3168,13 @@
         <v>38</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2867,13 +3185,13 @@
         <v>38</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2884,13 +3202,13 @@
         <v>38</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -2901,13 +3219,13 @@
         <v>38</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -2918,13 +3236,13 @@
         <v>38</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -2935,13 +3253,13 @@
         <v>38</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
@@ -2952,13 +3270,13 @@
         <v>38</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
@@ -2969,13 +3287,13 @@
         <v>38</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -2986,13 +3304,13 @@
         <v>43</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3003,13 +3321,13 @@
         <v>43</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3020,13 +3338,13 @@
         <v>43</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
@@ -3037,13 +3355,13 @@
         <v>43</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
@@ -3054,13 +3372,13 @@
         <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
@@ -3071,13 +3389,13 @@
         <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
@@ -3088,13 +3406,13 @@
         <v>43</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3105,13 +3423,13 @@
         <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
@@ -3122,13 +3440,13 @@
         <v>43</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
@@ -3139,13 +3457,13 @@
         <v>43</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
@@ -3156,13 +3474,13 @@
         <v>43</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
@@ -3173,13 +3491,13 @@
         <v>43</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -3190,13 +3508,13 @@
         <v>43</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -3207,16 +3525,16 @@
         <v>43</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -3227,13 +3545,13 @@
         <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -3244,13 +3562,13 @@
         <v>43</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -3261,13 +3579,13 @@
         <v>43</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>156</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -3278,13 +3596,13 @@
         <v>43</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -3295,13 +3613,13 @@
         <v>43</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -3312,13 +3630,13 @@
         <v>43</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>162</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -3329,13 +3647,13 @@
         <v>43</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3346,13 +3664,13 @@
         <v>43</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -3363,16 +3681,16 @@
         <v>43</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3383,13 +3701,13 @@
         <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3400,16 +3718,16 @@
         <v>43</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -3420,13 +3738,13 @@
         <v>43</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -3437,16 +3755,16 @@
         <v>43</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -3457,13 +3775,13 @@
         <v>43</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -3474,13 +3792,13 @@
         <v>43</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -3491,16 +3809,16 @@
         <v>43</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -3511,16 +3829,16 @@
         <v>43</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -3531,13 +3849,13 @@
         <v>43</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -3548,16 +3866,16 @@
         <v>43</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -3568,13 +3886,13 @@
         <v>43</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -3585,16 +3903,16 @@
         <v>43</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -3605,16 +3923,16 @@
         <v>43</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -3625,16 +3943,16 @@
         <v>43</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -3645,13 +3963,13 @@
         <v>43</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -3662,13 +3980,13 @@
         <v>59</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>193</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -3679,16 +3997,16 @@
         <v>59</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -3699,16 +4017,16 @@
         <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -3719,13 +4037,13 @@
         <v>59</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -3736,13 +4054,13 @@
         <v>60</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -3753,13 +4071,13 @@
         <v>60</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -3770,13 +4088,13 @@
         <v>60</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -3787,16 +4105,16 @@
         <v>60</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -3807,16 +4125,16 @@
         <v>60</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -3827,13 +4145,13 @@
         <v>60</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -3844,13 +4162,13 @@
         <v>60</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -3861,13 +4179,13 @@
         <v>60</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>210</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -3878,13 +4196,13 @@
         <v>60</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -3895,13 +4213,13 @@
         <v>60</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>195</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -3912,13 +4230,13 @@
         <v>60</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -3929,16 +4247,16 @@
         <v>60</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -3949,13 +4267,13 @@
         <v>60</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -3966,16 +4284,16 @@
         <v>60</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -3986,13 +4304,13 @@
         <v>60</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>220</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -4003,13 +4321,13 @@
         <v>60</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -4020,13 +4338,13 @@
         <v>60</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>223</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -4037,13 +4355,13 @@
         <v>60</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -4054,13 +4372,13 @@
         <v>60</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -4071,16 +4389,16 @@
         <v>60</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -4091,16 +4409,16 @@
         <v>60</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -4111,13 +4429,13 @@
         <v>60</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -4128,16 +4446,16 @@
         <v>60</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -4148,13 +4466,13 @@
         <v>60</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>234</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -4165,16 +4483,16 @@
         <v>60</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>236</v>
+        <v>32</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -4185,13 +4503,13 @@
         <v>60</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -4202,16 +4520,16 @@
         <v>60</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -4222,16 +4540,16 @@
         <v>60</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -4242,13 +4560,13 @@
         <v>60</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -4259,13 +4577,13 @@
         <v>75</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>243</v>
+        <v>42</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -4276,16 +4594,16 @@
         <v>75</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>245</v>
+        <v>89</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -4296,16 +4614,16 @@
         <v>75</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>245</v>
+        <v>89</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -4316,13 +4634,13 @@
         <v>75</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -4333,13 +4651,13 @@
         <v>75</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>250</v>
+        <v>78</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4350,13 +4668,13 @@
         <v>75</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -4367,13 +4685,13 @@
         <v>75</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>253</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -4384,13 +4702,13 @@
         <v>75</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>255</v>
+        <v>97</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -4401,16 +4719,16 @@
         <v>75</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>257</v>
+        <v>55</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -4421,16 +4739,16 @@
         <v>75</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>259</v>
+        <v>110</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -4441,13 +4759,13 @@
         <v>75</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>261</v>
+        <v>51</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -4458,13 +4776,13 @@
         <v>75</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>263</v>
+        <v>59</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -4475,16 +4793,16 @@
         <v>75</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>245</v>
+        <v>89</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -4495,13 +4813,13 @@
         <v>75</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -4512,13 +4830,13 @@
         <v>75</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>267</v>
+        <v>104</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4529,13 +4847,13 @@
         <v>75</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>269</v>
+        <v>106</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -4546,13 +4864,13 @@
         <v>75</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>271</v>
+        <v>107</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -4563,13 +4881,13 @@
         <v>75</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>273</v>
+        <v>93</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -4580,16 +4898,16 @@
         <v>75</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>275</v>
+        <v>102</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -4600,13 +4918,13 @@
         <v>75</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>275</v>
+        <v>102</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -4614,22 +4932,25 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C160" s="1">
         <v>104</v>
       </c>
+      <c r="D160" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="E160" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -4637,19 +4958,19 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>281</v>
+        <v>91</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -4657,19 +4978,19 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -7196,7 +7517,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>歌曲彙總!$B$1:$B$106</xm:f>
+            <xm:f>#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F998</xm:sqref>
         </x14:dataValidation>
@@ -7207,1182 +7528,1496 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E60A0B7D-38BA-492A-A950-EB4DA6E8AAB1}">
+  <dimension ref="A1:E106"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C5" t="s">
+        <v>403</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C6" t="s">
+        <v>405</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" t="s">
+        <v>413</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" t="s">
+        <v>412</v>
+      </c>
+      <c r="C11" t="s">
+        <v>414</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C12" t="s">
+        <v>416</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B13" t="s">
+        <v>417</v>
+      </c>
+      <c r="C13" t="s">
+        <v>411</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" t="s">
+        <v>420</v>
+      </c>
+      <c r="C15" t="s">
+        <v>421</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>308</v>
+      </c>
+      <c r="B16" t="s">
+        <v>422</v>
+      </c>
+      <c r="C16" t="s">
+        <v>423</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>368</v>
+      </c>
+      <c r="B17" t="s">
+        <v>424</v>
+      </c>
+      <c r="C17" t="s">
+        <v>425</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>376</v>
+      </c>
+      <c r="B18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C18" t="s">
+        <v>427</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>428</v>
+      </c>
+      <c r="C19" t="s">
+        <v>429</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B20" t="s">
+        <v>430</v>
+      </c>
+      <c r="C20" t="s">
+        <v>431</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" t="s">
+        <v>432</v>
+      </c>
+      <c r="C21" t="s">
+        <v>433</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>346</v>
+      </c>
+      <c r="B22" t="s">
+        <v>434</v>
+      </c>
+      <c r="C22" t="s">
+        <v>435</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" t="s">
+        <v>436</v>
+      </c>
+      <c r="C23" t="s">
+        <v>437</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>352</v>
+      </c>
+      <c r="B24" t="s">
+        <v>438</v>
+      </c>
+      <c r="C24" t="s">
+        <v>403</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>377</v>
+      </c>
+      <c r="B25" t="s">
+        <v>439</v>
+      </c>
+      <c r="C25" t="s">
+        <v>440</v>
+      </c>
+      <c r="E25" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B26" t="s">
+        <v>441</v>
+      </c>
+      <c r="C26" t="s">
+        <v>442</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>345</v>
+      </c>
+      <c r="B27" t="s">
+        <v>443</v>
+      </c>
+      <c r="C27" t="s">
+        <v>444</v>
+      </c>
+      <c r="E27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>304</v>
+      </c>
+      <c r="B28" t="s">
+        <v>445</v>
+      </c>
+      <c r="C28" t="s">
+        <v>411</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B29" t="s">
+        <v>446</v>
+      </c>
+      <c r="C29" t="s">
+        <v>447</v>
+      </c>
+      <c r="E29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>373</v>
+      </c>
+      <c r="B30" t="s">
+        <v>448</v>
+      </c>
+      <c r="C30" t="s">
+        <v>449</v>
+      </c>
+      <c r="E30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>362</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B31" t="s">
+        <v>450</v>
+      </c>
+      <c r="C31" t="s">
+        <v>451</v>
+      </c>
+      <c r="E31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>307</v>
+      </c>
+      <c r="B32" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" t="s">
+        <v>453</v>
+      </c>
+      <c r="E32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>359</v>
+      </c>
+      <c r="B33" t="s">
+        <v>454</v>
+      </c>
+      <c r="C33" t="s">
+        <v>403</v>
+      </c>
+      <c r="E33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>382</v>
+      </c>
+      <c r="B34" t="s">
+        <v>455</v>
+      </c>
+      <c r="C34" t="s">
+        <v>456</v>
+      </c>
+      <c r="E34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>378</v>
+      </c>
+      <c r="B35" t="s">
+        <v>457</v>
+      </c>
+      <c r="C35" t="s">
+        <v>458</v>
+      </c>
+      <c r="E35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>305</v>
+      </c>
+      <c r="B36" t="s">
+        <v>459</v>
+      </c>
+      <c r="C36" t="s">
+        <v>411</v>
+      </c>
+      <c r="E36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>334</v>
+      </c>
+      <c r="B37" t="s">
+        <v>460</v>
+      </c>
+      <c r="C37" t="s">
+        <v>413</v>
+      </c>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>299</v>
+      </c>
+      <c r="B38" t="s">
+        <v>461</v>
+      </c>
+      <c r="C38" t="s">
+        <v>462</v>
+      </c>
+      <c r="E38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>324</v>
+      </c>
+      <c r="B39" t="s">
+        <v>463</v>
+      </c>
+      <c r="C39" t="s">
+        <v>405</v>
+      </c>
+      <c r="E39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>336</v>
+      </c>
+      <c r="B40" t="s">
+        <v>464</v>
+      </c>
+      <c r="C40" t="s">
+        <v>444</v>
+      </c>
+      <c r="E40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>314</v>
+      </c>
+      <c r="B41" t="s">
+        <v>465</v>
+      </c>
+      <c r="C41" t="s">
+        <v>405</v>
+      </c>
+      <c r="E41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" t="s">
+        <v>466</v>
+      </c>
+      <c r="C42" t="s">
+        <v>397</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>353</v>
+      </c>
+      <c r="B43" t="s">
+        <v>467</v>
+      </c>
+      <c r="C43" t="s">
+        <v>431</v>
+      </c>
+      <c r="E43" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>386</v>
+      </c>
+      <c r="B44" t="s">
+        <v>468</v>
+      </c>
+      <c r="C44" t="s">
+        <v>469</v>
+      </c>
+      <c r="E44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>297</v>
+      </c>
+      <c r="B45" t="s">
+        <v>470</v>
+      </c>
+      <c r="C45" t="s">
+        <v>471</v>
+      </c>
+      <c r="E45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>331</v>
+      </c>
+      <c r="B46" t="s">
+        <v>472</v>
+      </c>
+      <c r="C46" t="s">
+        <v>473</v>
+      </c>
+      <c r="E46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>330</v>
+      </c>
+      <c r="B47" t="s">
+        <v>472</v>
+      </c>
+      <c r="C47" t="s">
+        <v>474</v>
+      </c>
+      <c r="E47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>384</v>
+      </c>
+      <c r="B48" t="s">
+        <v>475</v>
+      </c>
+      <c r="C48" t="s">
+        <v>427</v>
+      </c>
+      <c r="E48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>338</v>
+      </c>
+      <c r="B49" t="s">
+        <v>476</v>
+      </c>
+      <c r="C49" t="s">
+        <v>477</v>
+      </c>
+      <c r="E49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>300</v>
+      </c>
+      <c r="B50" t="s">
+        <v>478</v>
+      </c>
+      <c r="C50" t="s">
+        <v>479</v>
+      </c>
+      <c r="E50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>333</v>
+      </c>
+      <c r="B51" t="s">
+        <v>480</v>
+      </c>
+      <c r="C51" t="s">
+        <v>481</v>
+      </c>
+      <c r="E51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>387</v>
+      </c>
+      <c r="B52" t="s">
+        <v>482</v>
+      </c>
+      <c r="C52" t="s">
+        <v>411</v>
+      </c>
+      <c r="E52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>328</v>
+      </c>
+      <c r="B53" t="s">
+        <v>483</v>
+      </c>
+      <c r="C53" t="s">
+        <v>484</v>
+      </c>
+      <c r="E53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>311</v>
+      </c>
+      <c r="B54" t="s">
+        <v>485</v>
+      </c>
+      <c r="C54" t="s">
+        <v>486</v>
+      </c>
+      <c r="E54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>320</v>
+      </c>
+      <c r="B55" t="s">
+        <v>487</v>
+      </c>
+      <c r="C55" t="s">
+        <v>488</v>
+      </c>
+      <c r="E55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>337</v>
+      </c>
+      <c r="B56" t="s">
+        <v>489</v>
+      </c>
+      <c r="C56" t="s">
+        <v>403</v>
+      </c>
+      <c r="E56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>375</v>
+      </c>
+      <c r="B57" t="s">
+        <v>490</v>
+      </c>
+      <c r="C57" t="s">
+        <v>431</v>
+      </c>
+      <c r="E57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>332</v>
+      </c>
+      <c r="B58" t="s">
+        <v>491</v>
+      </c>
+      <c r="C58" t="s">
+        <v>492</v>
+      </c>
+      <c r="E58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>355</v>
+      </c>
+      <c r="B59" t="s">
+        <v>493</v>
+      </c>
+      <c r="C59" t="s">
+        <v>494</v>
+      </c>
+      <c r="E59" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>342</v>
+      </c>
+      <c r="B60" t="s">
+        <v>495</v>
+      </c>
+      <c r="C60" t="s">
+        <v>431</v>
+      </c>
+      <c r="E60" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>335</v>
+      </c>
+      <c r="B61" t="s">
+        <v>496</v>
+      </c>
+      <c r="C61" t="s">
+        <v>497</v>
+      </c>
+      <c r="E61" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>358</v>
+      </c>
+      <c r="B62" t="s">
+        <v>498</v>
+      </c>
+      <c r="C62" t="s">
+        <v>403</v>
+      </c>
+      <c r="E62" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" t="s">
+        <v>499</v>
+      </c>
+      <c r="C63" t="s">
+        <v>447</v>
+      </c>
+      <c r="E63" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>303</v>
+      </c>
+      <c r="B64" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" t="s">
+        <v>411</v>
+      </c>
+      <c r="E64" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>318</v>
+      </c>
+      <c r="B65" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" t="s">
+        <v>502</v>
+      </c>
+      <c r="E65" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>372</v>
+      </c>
+      <c r="B66" t="s">
+        <v>503</v>
+      </c>
+      <c r="C66" t="s">
+        <v>413</v>
+      </c>
+      <c r="E66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>366</v>
+      </c>
+      <c r="B67" t="s">
+        <v>504</v>
+      </c>
+      <c r="C67" t="s">
+        <v>505</v>
+      </c>
+      <c r="E67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>374</v>
+      </c>
+      <c r="B68" t="s">
+        <v>506</v>
+      </c>
+      <c r="C68" t="s">
+        <v>507</v>
+      </c>
+      <c r="E68" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>351</v>
+      </c>
+      <c r="B69" t="s">
+        <v>508</v>
+      </c>
+      <c r="C69" t="s">
+        <v>509</v>
+      </c>
+      <c r="E69" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>292</v>
+      </c>
+      <c r="B70" t="s">
+        <v>510</v>
+      </c>
+      <c r="C70" t="s">
+        <v>502</v>
+      </c>
+      <c r="E70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>381</v>
+      </c>
+      <c r="B71" t="s">
+        <v>511</v>
+      </c>
+      <c r="C71" t="s">
+        <v>411</v>
+      </c>
+      <c r="E71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>348</v>
+      </c>
+      <c r="B72" t="s">
+        <v>512</v>
+      </c>
+      <c r="C72" t="s">
+        <v>513</v>
+      </c>
+      <c r="E72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>361</v>
+      </c>
+      <c r="B73" t="s">
+        <v>514</v>
+      </c>
+      <c r="C73" t="s">
+        <v>479</v>
+      </c>
+      <c r="E73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>294</v>
+      </c>
+      <c r="B74" t="s">
+        <v>515</v>
+      </c>
+      <c r="C74" t="s">
+        <v>516</v>
+      </c>
+      <c r="E74" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>315</v>
+      </c>
+      <c r="B75" t="s">
+        <v>517</v>
+      </c>
+      <c r="C75" t="s">
+        <v>405</v>
+      </c>
+      <c r="E75" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>340</v>
+      </c>
+      <c r="B76" t="s">
+        <v>518</v>
+      </c>
+      <c r="C76" t="s">
+        <v>431</v>
+      </c>
+      <c r="E76" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>291</v>
+      </c>
+      <c r="B77" t="s">
+        <v>519</v>
+      </c>
+      <c r="C77" t="s">
+        <v>520</v>
+      </c>
+      <c r="E77" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>350</v>
+      </c>
+      <c r="B78" t="s">
+        <v>521</v>
+      </c>
+      <c r="C78" t="s">
+        <v>522</v>
+      </c>
+      <c r="E78" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>329</v>
+      </c>
+      <c r="B79" t="s">
+        <v>523</v>
+      </c>
+      <c r="C79" t="s">
+        <v>524</v>
+      </c>
+      <c r="E79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>290</v>
+      </c>
+      <c r="B80" t="s">
+        <v>525</v>
+      </c>
+      <c r="C80" t="s">
+        <v>526</v>
+      </c>
+      <c r="E80" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>289</v>
+      </c>
+      <c r="B81" t="s">
+        <v>527</v>
+      </c>
+      <c r="C81" t="s">
+        <v>528</v>
+      </c>
+      <c r="E81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>379</v>
+      </c>
+      <c r="B82" t="s">
+        <v>529</v>
+      </c>
+      <c r="C82" t="s">
+        <v>530</v>
+      </c>
+      <c r="E82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>309</v>
+      </c>
+      <c r="B83" t="s">
+        <v>531</v>
+      </c>
+      <c r="C83" t="s">
+        <v>532</v>
+      </c>
+      <c r="E83" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>393</v>
+      </c>
+      <c r="B84" t="s">
+        <v>533</v>
+      </c>
+      <c r="C84" t="s">
+        <v>534</v>
+      </c>
+      <c r="E84" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>319</v>
+      </c>
+      <c r="B85" t="s">
+        <v>535</v>
+      </c>
+      <c r="C85" t="s">
+        <v>536</v>
+      </c>
+      <c r="E85" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>391</v>
+      </c>
+      <c r="B86" t="s">
+        <v>537</v>
+      </c>
+      <c r="C86" t="s">
+        <v>538</v>
+      </c>
+      <c r="E86" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>317</v>
+      </c>
+      <c r="B87" t="s">
+        <v>539</v>
+      </c>
+      <c r="C87" t="s">
+        <v>528</v>
+      </c>
+      <c r="E87" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>296</v>
+      </c>
+      <c r="B88" t="s">
+        <v>540</v>
+      </c>
+      <c r="C88" t="s">
+        <v>541</v>
+      </c>
+      <c r="E88" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>295</v>
+      </c>
+      <c r="B89" t="s">
+        <v>542</v>
+      </c>
+      <c r="C89" t="s">
+        <v>543</v>
+      </c>
+      <c r="E89" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>383</v>
+      </c>
+      <c r="B90" t="s">
+        <v>544</v>
+      </c>
+      <c r="C90" t="s">
+        <v>545</v>
+      </c>
+      <c r="E90" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>322</v>
+      </c>
+      <c r="B91" t="s">
+        <v>546</v>
+      </c>
+      <c r="C91" t="s">
+        <v>547</v>
+      </c>
+      <c r="E91" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>313</v>
+      </c>
+      <c r="B92" t="s">
+        <v>548</v>
+      </c>
+      <c r="C92" t="s">
+        <v>549</v>
+      </c>
+      <c r="E92" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>357</v>
+      </c>
+      <c r="B93" t="s">
+        <v>550</v>
+      </c>
+      <c r="C93" t="s">
+        <v>551</v>
+      </c>
+      <c r="E93" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>326</v>
+      </c>
+      <c r="B94" t="s">
+        <v>552</v>
+      </c>
+      <c r="C94" t="s">
+        <v>553</v>
+      </c>
+      <c r="E94" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>392</v>
+      </c>
+      <c r="B95" t="s">
+        <v>554</v>
+      </c>
+      <c r="C95" t="s">
+        <v>555</v>
+      </c>
+      <c r="E95" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>316</v>
+      </c>
+      <c r="B96" t="s">
+        <v>556</v>
+      </c>
+      <c r="C96" t="s">
+        <v>528</v>
+      </c>
+      <c r="E96" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>388</v>
+      </c>
+      <c r="B97" t="s">
+        <v>557</v>
+      </c>
+      <c r="C97" t="s">
+        <v>558</v>
+      </c>
+      <c r="E97" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>321</v>
+      </c>
+      <c r="B98" t="s">
+        <v>559</v>
+      </c>
+      <c r="C98" t="s">
+        <v>560</v>
+      </c>
+      <c r="E98" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>389</v>
+      </c>
+      <c r="B99" t="s">
+        <v>561</v>
+      </c>
+      <c r="C99" t="s">
+        <v>562</v>
+      </c>
+      <c r="E99" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="B100" t="s">
+        <v>563</v>
+      </c>
+      <c r="C100" t="s">
+        <v>564</v>
+      </c>
+      <c r="E100" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>323</v>
+      </c>
+      <c r="B101" t="s">
+        <v>565</v>
+      </c>
+      <c r="C101" t="s">
+        <v>566</v>
+      </c>
+      <c r="E101" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
         <v>325</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="B102" t="s">
+        <v>567</v>
+      </c>
+      <c r="C102" t="s">
+        <v>568</v>
+      </c>
+      <c r="E102" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>385</v>
+      </c>
+      <c r="B103" t="s">
+        <v>569</v>
+      </c>
+      <c r="C103" t="s">
+        <v>570</v>
+      </c>
+      <c r="E103" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>310</v>
+      </c>
+      <c r="B104" t="s">
+        <v>571</v>
+      </c>
+      <c r="C104" t="s">
+        <v>549</v>
+      </c>
+      <c r="E104" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
         <v>356</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="B105" t="s">
+        <v>572</v>
+      </c>
+      <c r="C105" t="s">
+        <v>573</v>
+      </c>
+      <c r="E105" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
         <v>312</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A98" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A99" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A101" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A103" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A104" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A105" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A106" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>469</v>
+      <c r="B106" t="s">
+        <v>574</v>
+      </c>
+      <c r="C106" t="s">
+        <v>575</v>
+      </c>
+      <c r="E106" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/song_records.xlsx
+++ b/song_records.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\73415\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\TOP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B93B969B-27B4-4F4F-B42A-632F7BA9EA26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18870" windowHeight="6855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18015" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
-    <sheet name="歌曲彙總" sheetId="3" r:id="rId2"/>
+    <sheet name="歌曲彙總" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="593">
   <si>
     <t>id</t>
   </si>
@@ -87,6 +86,9 @@
     <t>半句再見（zh4）</t>
   </si>
   <si>
+    <t>甲乙丙丁（zh61）</t>
+  </si>
+  <si>
     <t>白日（ja21）</t>
   </si>
   <si>
@@ -138,12 +140,21 @@
     <t>我的歌聲裡（zh49）</t>
   </si>
   <si>
+    <t>Cover</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
+  </si>
+  <si>
     <t>我是恁老爸（nan6）</t>
   </si>
   <si>
     <t>我們不一樣（zh13）</t>
   </si>
   <si>
+    <t>我們都傻（zh59）</t>
+  </si>
+  <si>
     <t>我想我不會愛你（zh39）</t>
   </si>
   <si>
@@ -162,6 +173,9 @@
     <t>孤獨的總和（zh6）</t>
   </si>
   <si>
+    <t>幸福在歌唱（zh60）</t>
+  </si>
+  <si>
     <t>怪獣の花唄（ja16）</t>
   </si>
   <si>
@@ -174,9 +188,15 @@
     <t>知道（zh24）</t>
   </si>
   <si>
+    <t>BAD GUY（en1）</t>
+  </si>
+  <si>
     <t>雨愛（zh37）</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
+  </si>
+  <si>
     <t>変わらないもの（ja26）</t>
   </si>
   <si>
@@ -210,6 +230,12 @@
     <t>鬼ノ宴(Demons Banquet)（ja7）</t>
   </si>
   <si>
+    <t>ACT/アクト（ja1）</t>
+  </si>
+  <si>
+    <t>7:16</t>
+  </si>
+  <si>
     <t>偽顏（ja12）</t>
   </si>
   <si>
@@ -234,6 +260,12 @@
     <t>渺小（zh38）</t>
   </si>
   <si>
+    <t>藍（zh2）</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
     <t>買你（zh8）</t>
   </si>
   <si>
@@ -258,6 +290,9 @@
     <t>路過人間（zh3）</t>
   </si>
   <si>
+    <t>17:34</t>
+  </si>
+  <si>
     <t>遇見（zh55）</t>
   </si>
   <si>
@@ -276,7 +311,7 @@
     <t>曖昧（zh25）</t>
   </si>
   <si>
-    <t>藍（zh2）</t>
+    <t>21:56</t>
   </si>
   <si>
     <t>聽見下雨的聲音（zh35）</t>
@@ -285,18 +320,15 @@
     <t>體面（zh17）</t>
   </si>
   <si>
-    <t>ACT/アクト（ja1）</t>
-  </si>
-  <si>
-    <t>BAD GUY（en1）</t>
-  </si>
-  <si>
     <t>Breathe（ko1）</t>
   </si>
   <si>
     <t>Bunny Girl（ja5）</t>
   </si>
   <si>
+    <t>26:23</t>
+  </si>
+  <si>
     <t>Bのリベンジ（ja32）</t>
   </si>
   <si>
@@ -315,6 +347,9 @@
     <t>JANE DOE（ja2）</t>
   </si>
   <si>
+    <t>32:29</t>
+  </si>
+  <si>
     <t>Miniskirt（ko2）</t>
   </si>
   <si>
@@ -330,6 +365,12 @@
     <t>Santé（zh16）</t>
   </si>
   <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>33:52</t>
+  </si>
+  <si>
     <t>the WORLD（ja31）</t>
   </si>
   <si>
@@ -348,6 +389,9 @@
     <t>たばこ（ja29）</t>
   </si>
   <si>
+    <t>34:58</t>
+  </si>
+  <si>
     <t>どうせ無くなるだけ（ja15）</t>
   </si>
   <si>
@@ -366,42 +410,6 @@
     <t>ほろよい（ja8）</t>
   </si>
   <si>
-    <t>Cover</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
-  </si>
-  <si>
-    <t>7:16</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>17:34</t>
-  </si>
-  <si>
-    <t>21:56</t>
-  </si>
-  <si>
-    <t>26:23</t>
-  </si>
-  <si>
-    <t>32:29</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>33:52</t>
-  </si>
-  <si>
-    <t>34:58</t>
-  </si>
-  <si>
     <t>37:38</t>
   </si>
   <si>
@@ -888,6 +896,30 @@
     <t>神崎アルファ</t>
   </si>
   <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>21:53</t>
+  </si>
+  <si>
+    <t>34:29</t>
+  </si>
+  <si>
+    <t>43:41</t>
+  </si>
+  <si>
+    <t>54:27</t>
+  </si>
+  <si>
+    <t>1:01:38</t>
+  </si>
+  <si>
+    <t>1:08:08</t>
+  </si>
+  <si>
+    <t>1:22:28</t>
+  </si>
+  <si>
     <t>zh1</t>
   </si>
   <si>
@@ -1206,6 +1238,15 @@
     <t>ja32</t>
   </si>
   <si>
+    <t>zh59</t>
+  </si>
+  <si>
+    <t>zh60</t>
+  </si>
+  <si>
+    <t>zh61</t>
+  </si>
+  <si>
     <t>一支小雨傘</t>
   </si>
   <si>
@@ -1278,6 +1319,12 @@
     <t>半句再見</t>
   </si>
   <si>
+    <t>甲乙丙丁</t>
+  </si>
+  <si>
+    <t>李佳薇</t>
+  </si>
+  <si>
     <t>白日</t>
   </si>
   <si>
@@ -1386,6 +1433,9 @@
     <t>大壯</t>
   </si>
   <si>
+    <t>我們都傻</t>
+  </si>
+  <si>
     <t>我想我不會愛你</t>
   </si>
   <si>
@@ -1413,6 +1463,9 @@
     <t>吳汶芳</t>
   </si>
   <si>
+    <t>幸福在歌唱</t>
+  </si>
+  <si>
     <t>怪獣の花唄</t>
   </si>
   <si>
@@ -1561,9 +1614,6 @@
   </si>
   <si>
     <t>像天堂的懸崖</t>
-  </si>
-  <si>
-    <t>李佳薇</t>
   </si>
   <si>
     <t>夢醒時分</t>
@@ -1755,7 +1805,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -2028,7 +2078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2070,13 +2120,13 @@
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -2084,17 +2134,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -2102,17 +2152,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -2123,13 +2173,13 @@
         <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -2140,13 +2190,13 @@
         <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -2157,13 +2207,13 @@
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -2174,10 +2224,10 @@
         <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>20</v>
@@ -2191,13 +2241,13 @@
         <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -2208,16 +2258,16 @@
         <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -2228,16 +2278,16 @@
         <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -2248,16 +2298,16 @@
         <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -2268,16 +2318,16 @@
         <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -2288,16 +2338,16 @@
         <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -2308,16 +2358,16 @@
         <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -2328,16 +2378,16 @@
         <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -2348,13 +2398,13 @@
         <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -2365,13 +2415,13 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -2382,16 +2432,16 @@
         <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -2402,13 +2452,13 @@
         <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -2419,13 +2469,13 @@
         <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -2436,13 +2486,13 @@
         <v>24</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -2453,16 +2503,16 @@
         <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -2473,13 +2523,13 @@
         <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -2490,13 +2540,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -2507,13 +2557,13 @@
         <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -2524,16 +2574,16 @@
         <v>38</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -2544,16 +2594,16 @@
         <v>38</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -2564,13 +2614,13 @@
         <v>38</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -2581,16 +2631,16 @@
         <v>38</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -2601,16 +2651,16 @@
         <v>38</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -2621,16 +2671,16 @@
         <v>38</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -2641,16 +2691,16 @@
         <v>38</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -2661,16 +2711,16 @@
         <v>38</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -2681,13 +2731,13 @@
         <v>38</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -2698,13 +2748,13 @@
         <v>38</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -2715,13 +2765,13 @@
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -2732,13 +2782,13 @@
         <v>38</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -2749,13 +2799,13 @@
         <v>38</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -2766,13 +2816,13 @@
         <v>38</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -2783,16 +2833,16 @@
         <v>38</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -2803,16 +2853,16 @@
         <v>38</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -2823,13 +2873,13 @@
         <v>38</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -2840,16 +2890,16 @@
         <v>38</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -2860,16 +2910,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -2880,16 +2930,16 @@
         <v>38</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -2900,13 +2950,13 @@
         <v>38</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -2917,13 +2967,13 @@
         <v>38</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -2934,16 +2984,16 @@
         <v>38</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -2954,16 +3004,16 @@
         <v>38</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -2974,16 +3024,16 @@
         <v>38</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -2994,13 +3044,13 @@
         <v>38</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -3011,16 +3061,16 @@
         <v>38</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -3031,16 +3081,16 @@
         <v>38</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -3051,16 +3101,16 @@
         <v>38</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -3071,16 +3121,16 @@
         <v>38</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -3091,16 +3141,16 @@
         <v>38</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -3111,13 +3161,13 @@
         <v>38</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -3128,16 +3178,16 @@
         <v>38</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -3148,16 +3198,16 @@
         <v>38</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -3168,13 +3218,13 @@
         <v>38</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -3185,13 +3235,13 @@
         <v>38</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -3202,13 +3252,13 @@
         <v>38</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -3219,13 +3269,13 @@
         <v>38</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -3236,13 +3286,13 @@
         <v>38</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -3253,10 +3303,10 @@
         <v>38</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>20</v>
@@ -3270,13 +3320,13 @@
         <v>38</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
@@ -3287,13 +3337,13 @@
         <v>38</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
@@ -3304,13 +3354,13 @@
         <v>43</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
@@ -3321,13 +3371,13 @@
         <v>43</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3338,13 +3388,13 @@
         <v>43</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
@@ -3355,13 +3405,13 @@
         <v>43</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
@@ -3372,13 +3422,13 @@
         <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
@@ -3389,13 +3439,13 @@
         <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
@@ -3406,13 +3456,13 @@
         <v>43</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -3423,10 +3473,10 @@
         <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>12</v>
@@ -3440,13 +3490,13 @@
         <v>43</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
@@ -3457,10 +3507,10 @@
         <v>43</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>14</v>
@@ -3474,10 +3524,10 @@
         <v>43</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>15</v>
@@ -3491,13 +3541,13 @@
         <v>43</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
@@ -3508,13 +3558,13 @@
         <v>43</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
@@ -3525,16 +3575,16 @@
         <v>43</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -3545,10 +3595,10 @@
         <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>9</v>
@@ -3562,13 +3612,13 @@
         <v>43</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -3579,13 +3629,13 @@
         <v>43</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -3596,13 +3646,13 @@
         <v>43</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -3613,13 +3663,13 @@
         <v>43</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
@@ -3630,13 +3680,13 @@
         <v>43</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
@@ -3647,13 +3697,13 @@
         <v>43</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3664,13 +3714,13 @@
         <v>43</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -3681,16 +3731,16 @@
         <v>43</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3701,13 +3751,13 @@
         <v>43</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3718,16 +3768,16 @@
         <v>43</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
@@ -3738,13 +3788,13 @@
         <v>43</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
@@ -3755,16 +3805,16 @@
         <v>43</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
@@ -3775,13 +3825,13 @@
         <v>43</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -3792,13 +3842,13 @@
         <v>43</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -3809,16 +3859,16 @@
         <v>43</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -3829,16 +3879,16 @@
         <v>43</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -3849,13 +3899,13 @@
         <v>43</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -3866,16 +3916,16 @@
         <v>43</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -3886,13 +3936,13 @@
         <v>43</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -3903,16 +3953,16 @@
         <v>43</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -3923,16 +3973,16 @@
         <v>43</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -3943,16 +3993,16 @@
         <v>43</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -3963,13 +4013,13 @@
         <v>43</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -3980,10 +4030,10 @@
         <v>59</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>11</v>
@@ -3997,16 +4047,16 @@
         <v>59</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -4017,16 +4067,16 @@
         <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>18</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -4037,13 +4087,13 @@
         <v>59</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -4054,13 +4104,13 @@
         <v>60</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -4071,13 +4121,13 @@
         <v>60</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -4088,13 +4138,13 @@
         <v>60</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -4105,16 +4155,16 @@
         <v>60</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -4125,16 +4175,16 @@
         <v>60</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -4145,13 +4195,13 @@
         <v>60</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -4162,13 +4212,13 @@
         <v>60</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -4179,13 +4229,13 @@
         <v>60</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -4196,10 +4246,10 @@
         <v>60</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>17</v>
@@ -4213,10 +4263,10 @@
         <v>60</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>18</v>
@@ -4230,13 +4280,13 @@
         <v>60</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -4247,16 +4297,16 @@
         <v>60</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -4267,10 +4317,10 @@
         <v>60</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>19</v>
@@ -4284,16 +4334,16 @@
         <v>60</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -4304,13 +4354,13 @@
         <v>60</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
@@ -4321,13 +4371,13 @@
         <v>60</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
@@ -4338,13 +4388,13 @@
         <v>60</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
@@ -4355,13 +4405,13 @@
         <v>60</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -4372,13 +4422,13 @@
         <v>60</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -4389,16 +4439,16 @@
         <v>60</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -4409,16 +4459,16 @@
         <v>60</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -4429,13 +4479,13 @@
         <v>60</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -4446,16 +4496,16 @@
         <v>60</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -4466,13 +4516,13 @@
         <v>60</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -4483,16 +4533,16 @@
         <v>60</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -4503,13 +4553,13 @@
         <v>60</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
@@ -4520,16 +4570,16 @@
         <v>60</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
@@ -4540,16 +4590,16 @@
         <v>60</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -4560,13 +4610,13 @@
         <v>60</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
@@ -4577,13 +4627,13 @@
         <v>75</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -4594,16 +4644,16 @@
         <v>75</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -4614,16 +4664,16 @@
         <v>75</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -4634,10 +4684,10 @@
         <v>75</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>16</v>
@@ -4651,13 +4701,13 @@
         <v>75</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4668,13 +4718,13 @@
         <v>75</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -4685,13 +4735,13 @@
         <v>75</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -4702,13 +4752,13 @@
         <v>75</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -4719,16 +4769,16 @@
         <v>75</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -4739,16 +4789,16 @@
         <v>75</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -4759,13 +4809,13 @@
         <v>75</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -4776,13 +4826,13 @@
         <v>75</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -4793,16 +4843,16 @@
         <v>75</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -4813,13 +4863,13 @@
         <v>75</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -4830,13 +4880,13 @@
         <v>75</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4847,13 +4897,13 @@
         <v>75</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -4864,13 +4914,13 @@
         <v>75</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -4881,13 +4931,13 @@
         <v>75</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -4898,16 +4948,16 @@
         <v>75</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -4918,13 +4968,13 @@
         <v>75</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -4932,25 +4982,25 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C160" s="1">
         <v>104</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -4958,19 +5008,19 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -4978,44 +5028,156 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="C163" s="1">
+        <v>124</v>
+      </c>
+      <c r="D163" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F162" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="H162" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F163" s="3"/>
+      <c r="E163" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F164" s="3"/>
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="C164" s="1">
+        <v>124</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F165" s="3"/>
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="C165" s="1">
+        <v>124</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F166" s="3"/>
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="C166" s="1">
+        <v>124</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F167" s="3"/>
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="C167" s="1">
+        <v>124</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F168" s="3"/>
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="C168" s="1">
+        <v>124</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F169" s="3"/>
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="C169" s="1">
+        <v>124</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F170" s="3"/>
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="C170" s="1">
+        <v>124</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="F171" s="3"/>
@@ -7504,20 +7666,20 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B160" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B161" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B162" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="B160" r:id="rId4"/>
+    <hyperlink ref="B161" r:id="rId5"/>
+    <hyperlink ref="B162" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>#REF!</xm:f>
+            <xm:f>歌曲彙總!$E$1:$E$106</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F998</xm:sqref>
         </x14:dataValidation>
@@ -7528,1496 +7690,4324 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E60A0B7D-38BA-492A-A950-EB4DA6E8AAB1}">
-  <dimension ref="A1:E106"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B15" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A74" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A76" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B93" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A100" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A105" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C2" t="s">
-        <v>397</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B4" t="s">
-        <v>400</v>
-      </c>
-      <c r="C4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" t="s">
-        <v>402</v>
-      </c>
-      <c r="C5" t="s">
-        <v>403</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>327</v>
-      </c>
-      <c r="B6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C6" t="s">
-        <v>405</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C7" t="s">
-        <v>407</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B8" t="s">
-        <v>408</v>
-      </c>
-      <c r="C8" t="s">
-        <v>409</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>380</v>
-      </c>
-      <c r="B9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>370</v>
-      </c>
-      <c r="B10" t="s">
-        <v>412</v>
-      </c>
-      <c r="C10" t="s">
-        <v>413</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>364</v>
-      </c>
-      <c r="B11" t="s">
-        <v>412</v>
-      </c>
-      <c r="C11" t="s">
-        <v>414</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>371</v>
-      </c>
-      <c r="B12" t="s">
-        <v>415</v>
-      </c>
-      <c r="C12" t="s">
-        <v>416</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>293</v>
-      </c>
-      <c r="B13" t="s">
-        <v>417</v>
-      </c>
-      <c r="C13" t="s">
-        <v>411</v>
-      </c>
-      <c r="E13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>354</v>
-      </c>
-      <c r="B14" t="s">
-        <v>418</v>
-      </c>
-      <c r="C14" t="s">
-        <v>419</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>306</v>
-      </c>
-      <c r="B15" t="s">
-        <v>420</v>
-      </c>
-      <c r="C15" t="s">
-        <v>421</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>308</v>
-      </c>
-      <c r="B16" t="s">
-        <v>422</v>
-      </c>
-      <c r="C16" t="s">
-        <v>423</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>368</v>
-      </c>
-      <c r="B17" t="s">
-        <v>424</v>
-      </c>
-      <c r="C17" t="s">
-        <v>425</v>
-      </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>376</v>
-      </c>
-      <c r="B18" t="s">
-        <v>426</v>
-      </c>
-      <c r="C18" t="s">
-        <v>427</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="B106" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B19" t="s">
-        <v>428</v>
-      </c>
-      <c r="C19" t="s">
-        <v>429</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B20" t="s">
-        <v>430</v>
-      </c>
-      <c r="C20" t="s">
-        <v>431</v>
-      </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" t="s">
-        <v>432</v>
-      </c>
-      <c r="C21" t="s">
-        <v>433</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>346</v>
-      </c>
-      <c r="B22" t="s">
-        <v>434</v>
-      </c>
-      <c r="C22" t="s">
-        <v>435</v>
-      </c>
-      <c r="E22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>369</v>
-      </c>
-      <c r="B23" t="s">
-        <v>436</v>
-      </c>
-      <c r="C23" t="s">
-        <v>437</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>352</v>
-      </c>
-      <c r="B24" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" t="s">
-        <v>403</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>377</v>
-      </c>
-      <c r="B25" t="s">
-        <v>439</v>
-      </c>
-      <c r="C25" t="s">
-        <v>440</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>298</v>
-      </c>
-      <c r="B26" t="s">
-        <v>441</v>
-      </c>
-      <c r="C26" t="s">
-        <v>442</v>
-      </c>
-      <c r="E26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>345</v>
-      </c>
-      <c r="B27" t="s">
-        <v>443</v>
-      </c>
-      <c r="C27" t="s">
-        <v>444</v>
-      </c>
-      <c r="E27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>304</v>
-      </c>
-      <c r="B28" t="s">
-        <v>445</v>
-      </c>
-      <c r="C28" t="s">
-        <v>411</v>
-      </c>
-      <c r="E28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>302</v>
-      </c>
-      <c r="B29" t="s">
-        <v>446</v>
-      </c>
-      <c r="C29" t="s">
-        <v>447</v>
-      </c>
-      <c r="E29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>373</v>
-      </c>
-      <c r="B30" t="s">
-        <v>448</v>
-      </c>
-      <c r="C30" t="s">
-        <v>449</v>
-      </c>
-      <c r="E30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B31" t="s">
-        <v>450</v>
-      </c>
-      <c r="C31" t="s">
-        <v>451</v>
-      </c>
-      <c r="E31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>307</v>
-      </c>
-      <c r="B32" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" t="s">
-        <v>453</v>
-      </c>
-      <c r="E32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>359</v>
-      </c>
-      <c r="B33" t="s">
-        <v>454</v>
-      </c>
-      <c r="C33" t="s">
-        <v>403</v>
-      </c>
-      <c r="E33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>382</v>
-      </c>
-      <c r="B34" t="s">
-        <v>455</v>
-      </c>
-      <c r="C34" t="s">
-        <v>456</v>
-      </c>
-      <c r="E34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>378</v>
-      </c>
-      <c r="B35" t="s">
-        <v>457</v>
-      </c>
-      <c r="C35" t="s">
-        <v>458</v>
-      </c>
-      <c r="E35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>305</v>
-      </c>
-      <c r="B36" t="s">
-        <v>459</v>
-      </c>
-      <c r="C36" t="s">
-        <v>411</v>
-      </c>
-      <c r="E36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>334</v>
-      </c>
-      <c r="B37" t="s">
-        <v>460</v>
-      </c>
-      <c r="C37" t="s">
-        <v>413</v>
-      </c>
-      <c r="E37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>299</v>
-      </c>
-      <c r="B38" t="s">
-        <v>461</v>
-      </c>
-      <c r="C38" t="s">
-        <v>462</v>
-      </c>
-      <c r="E38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>324</v>
-      </c>
-      <c r="B39" t="s">
-        <v>463</v>
-      </c>
-      <c r="C39" t="s">
-        <v>405</v>
-      </c>
-      <c r="E39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>336</v>
-      </c>
-      <c r="B40" t="s">
-        <v>464</v>
-      </c>
-      <c r="C40" t="s">
-        <v>444</v>
-      </c>
-      <c r="E40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>314</v>
-      </c>
-      <c r="B41" t="s">
-        <v>465</v>
-      </c>
-      <c r="C41" t="s">
-        <v>405</v>
-      </c>
-      <c r="E41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" t="s">
-        <v>466</v>
-      </c>
-      <c r="C42" t="s">
-        <v>397</v>
-      </c>
-      <c r="E42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>353</v>
-      </c>
-      <c r="B43" t="s">
-        <v>467</v>
-      </c>
-      <c r="C43" t="s">
-        <v>431</v>
-      </c>
-      <c r="E43" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>386</v>
-      </c>
-      <c r="B44" t="s">
-        <v>468</v>
-      </c>
-      <c r="C44" t="s">
-        <v>469</v>
-      </c>
-      <c r="E44" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>297</v>
-      </c>
-      <c r="B45" t="s">
-        <v>470</v>
-      </c>
-      <c r="C45" t="s">
-        <v>471</v>
-      </c>
-      <c r="E45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>331</v>
-      </c>
-      <c r="B46" t="s">
-        <v>472</v>
-      </c>
-      <c r="C46" t="s">
-        <v>473</v>
-      </c>
-      <c r="E46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>330</v>
-      </c>
-      <c r="B47" t="s">
-        <v>472</v>
-      </c>
-      <c r="C47" t="s">
-        <v>474</v>
-      </c>
-      <c r="E47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>384</v>
-      </c>
-      <c r="B48" t="s">
-        <v>475</v>
-      </c>
-      <c r="C48" t="s">
-        <v>427</v>
-      </c>
-      <c r="E48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>338</v>
-      </c>
-      <c r="B49" t="s">
-        <v>476</v>
-      </c>
-      <c r="C49" t="s">
-        <v>477</v>
-      </c>
-      <c r="E49" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>300</v>
-      </c>
-      <c r="B50" t="s">
-        <v>478</v>
-      </c>
-      <c r="C50" t="s">
-        <v>479</v>
-      </c>
-      <c r="E50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>333</v>
-      </c>
-      <c r="B51" t="s">
-        <v>480</v>
-      </c>
-      <c r="C51" t="s">
-        <v>481</v>
-      </c>
-      <c r="E51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>387</v>
-      </c>
-      <c r="B52" t="s">
-        <v>482</v>
-      </c>
-      <c r="C52" t="s">
-        <v>411</v>
-      </c>
-      <c r="E52" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>328</v>
-      </c>
-      <c r="B53" t="s">
-        <v>483</v>
-      </c>
-      <c r="C53" t="s">
-        <v>484</v>
-      </c>
-      <c r="E53" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>311</v>
-      </c>
-      <c r="B54" t="s">
-        <v>485</v>
-      </c>
-      <c r="C54" t="s">
-        <v>486</v>
-      </c>
-      <c r="E54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>320</v>
-      </c>
-      <c r="B55" t="s">
-        <v>487</v>
-      </c>
-      <c r="C55" t="s">
-        <v>488</v>
-      </c>
-      <c r="E55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>337</v>
-      </c>
-      <c r="B56" t="s">
-        <v>489</v>
-      </c>
-      <c r="C56" t="s">
-        <v>403</v>
-      </c>
-      <c r="E56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>375</v>
-      </c>
-      <c r="B57" t="s">
-        <v>490</v>
-      </c>
-      <c r="C57" t="s">
-        <v>431</v>
-      </c>
-      <c r="E57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>332</v>
-      </c>
-      <c r="B58" t="s">
-        <v>491</v>
-      </c>
-      <c r="C58" t="s">
-        <v>492</v>
-      </c>
-      <c r="E58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>355</v>
-      </c>
-      <c r="B59" t="s">
-        <v>493</v>
-      </c>
-      <c r="C59" t="s">
-        <v>494</v>
-      </c>
-      <c r="E59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>342</v>
-      </c>
-      <c r="B60" t="s">
-        <v>495</v>
-      </c>
-      <c r="C60" t="s">
-        <v>431</v>
-      </c>
-      <c r="E60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>335</v>
-      </c>
-      <c r="B61" t="s">
-        <v>496</v>
-      </c>
-      <c r="C61" t="s">
-        <v>497</v>
-      </c>
-      <c r="E61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>358</v>
-      </c>
-      <c r="B62" t="s">
-        <v>498</v>
-      </c>
-      <c r="C62" t="s">
-        <v>403</v>
-      </c>
-      <c r="E62" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>301</v>
-      </c>
-      <c r="B63" t="s">
-        <v>499</v>
-      </c>
-      <c r="C63" t="s">
-        <v>447</v>
-      </c>
-      <c r="E63" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>303</v>
-      </c>
-      <c r="B64" t="s">
-        <v>500</v>
-      </c>
-      <c r="C64" t="s">
-        <v>411</v>
-      </c>
-      <c r="E64" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>318</v>
-      </c>
-      <c r="B65" t="s">
-        <v>501</v>
-      </c>
-      <c r="C65" t="s">
-        <v>502</v>
-      </c>
-      <c r="E65" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>372</v>
-      </c>
-      <c r="B66" t="s">
-        <v>503</v>
-      </c>
-      <c r="C66" t="s">
-        <v>413</v>
-      </c>
-      <c r="E66" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>366</v>
-      </c>
-      <c r="B67" t="s">
-        <v>504</v>
-      </c>
-      <c r="C67" t="s">
-        <v>505</v>
-      </c>
-      <c r="E67" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>374</v>
-      </c>
-      <c r="B68" t="s">
-        <v>506</v>
-      </c>
-      <c r="C68" t="s">
-        <v>507</v>
-      </c>
-      <c r="E68" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>351</v>
-      </c>
-      <c r="B69" t="s">
-        <v>508</v>
-      </c>
-      <c r="C69" t="s">
-        <v>509</v>
-      </c>
-      <c r="E69" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>292</v>
-      </c>
-      <c r="B70" t="s">
-        <v>510</v>
-      </c>
-      <c r="C70" t="s">
-        <v>502</v>
-      </c>
-      <c r="E70" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>381</v>
-      </c>
-      <c r="B71" t="s">
-        <v>511</v>
-      </c>
-      <c r="C71" t="s">
-        <v>411</v>
-      </c>
-      <c r="E71" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>348</v>
-      </c>
-      <c r="B72" t="s">
-        <v>512</v>
-      </c>
-      <c r="C72" t="s">
-        <v>513</v>
-      </c>
-      <c r="E72" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>361</v>
-      </c>
-      <c r="B73" t="s">
-        <v>514</v>
-      </c>
-      <c r="C73" t="s">
-        <v>479</v>
-      </c>
-      <c r="E73" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>294</v>
-      </c>
-      <c r="B74" t="s">
-        <v>515</v>
-      </c>
-      <c r="C74" t="s">
-        <v>516</v>
-      </c>
-      <c r="E74" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>315</v>
-      </c>
-      <c r="B75" t="s">
-        <v>517</v>
-      </c>
-      <c r="C75" t="s">
-        <v>405</v>
-      </c>
-      <c r="E75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>340</v>
-      </c>
-      <c r="B76" t="s">
-        <v>518</v>
-      </c>
-      <c r="C76" t="s">
-        <v>431</v>
-      </c>
-      <c r="E76" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>291</v>
-      </c>
-      <c r="B77" t="s">
-        <v>519</v>
-      </c>
-      <c r="C77" t="s">
-        <v>520</v>
-      </c>
-      <c r="E77" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>350</v>
-      </c>
-      <c r="B78" t="s">
-        <v>521</v>
-      </c>
-      <c r="C78" t="s">
-        <v>522</v>
-      </c>
-      <c r="E78" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>329</v>
-      </c>
-      <c r="B79" t="s">
-        <v>523</v>
-      </c>
-      <c r="C79" t="s">
-        <v>524</v>
-      </c>
-      <c r="E79" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>290</v>
-      </c>
-      <c r="B80" t="s">
-        <v>525</v>
-      </c>
-      <c r="C80" t="s">
-        <v>526</v>
-      </c>
-      <c r="E80" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>289</v>
-      </c>
-      <c r="B81" t="s">
-        <v>527</v>
-      </c>
-      <c r="C81" t="s">
-        <v>528</v>
-      </c>
-      <c r="E81" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>379</v>
-      </c>
-      <c r="B82" t="s">
-        <v>529</v>
-      </c>
-      <c r="C82" t="s">
-        <v>530</v>
-      </c>
-      <c r="E82" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>309</v>
-      </c>
-      <c r="B83" t="s">
-        <v>531</v>
-      </c>
-      <c r="C83" t="s">
-        <v>532</v>
-      </c>
-      <c r="E83" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>393</v>
-      </c>
-      <c r="B84" t="s">
-        <v>533</v>
-      </c>
-      <c r="C84" t="s">
-        <v>534</v>
-      </c>
-      <c r="E84" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>319</v>
-      </c>
-      <c r="B85" t="s">
-        <v>535</v>
-      </c>
-      <c r="C85" t="s">
-        <v>536</v>
-      </c>
-      <c r="E85" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>391</v>
-      </c>
-      <c r="B86" t="s">
-        <v>537</v>
-      </c>
-      <c r="C86" t="s">
-        <v>538</v>
-      </c>
-      <c r="E86" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>317</v>
-      </c>
-      <c r="B87" t="s">
-        <v>539</v>
-      </c>
-      <c r="C87" t="s">
-        <v>528</v>
-      </c>
-      <c r="E87" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>296</v>
-      </c>
-      <c r="B88" t="s">
-        <v>540</v>
-      </c>
-      <c r="C88" t="s">
-        <v>541</v>
-      </c>
-      <c r="E88" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>295</v>
-      </c>
-      <c r="B89" t="s">
-        <v>542</v>
-      </c>
-      <c r="C89" t="s">
-        <v>543</v>
-      </c>
-      <c r="E89" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>383</v>
-      </c>
-      <c r="B90" t="s">
-        <v>544</v>
-      </c>
-      <c r="C90" t="s">
-        <v>545</v>
-      </c>
-      <c r="E90" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>322</v>
-      </c>
-      <c r="B91" t="s">
-        <v>546</v>
-      </c>
-      <c r="C91" t="s">
-        <v>547</v>
-      </c>
-      <c r="E91" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>313</v>
-      </c>
-      <c r="B92" t="s">
-        <v>548</v>
-      </c>
-      <c r="C92" t="s">
-        <v>549</v>
-      </c>
-      <c r="E92" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>357</v>
-      </c>
-      <c r="B93" t="s">
-        <v>550</v>
-      </c>
-      <c r="C93" t="s">
-        <v>551</v>
-      </c>
-      <c r="E93" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>326</v>
-      </c>
-      <c r="B94" t="s">
-        <v>552</v>
-      </c>
-      <c r="C94" t="s">
-        <v>553</v>
-      </c>
-      <c r="E94" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>392</v>
-      </c>
-      <c r="B95" t="s">
-        <v>554</v>
-      </c>
-      <c r="C95" t="s">
-        <v>555</v>
-      </c>
-      <c r="E95" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>316</v>
-      </c>
-      <c r="B96" t="s">
-        <v>556</v>
-      </c>
-      <c r="C96" t="s">
-        <v>528</v>
-      </c>
-      <c r="E96" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>388</v>
-      </c>
-      <c r="B97" t="s">
-        <v>557</v>
-      </c>
-      <c r="C97" t="s">
-        <v>558</v>
-      </c>
-      <c r="E97" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>321</v>
-      </c>
-      <c r="B98" t="s">
-        <v>559</v>
-      </c>
-      <c r="C98" t="s">
-        <v>560</v>
-      </c>
-      <c r="E98" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>389</v>
-      </c>
-      <c r="B99" t="s">
-        <v>561</v>
-      </c>
-      <c r="C99" t="s">
-        <v>562</v>
-      </c>
-      <c r="E99" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>390</v>
-      </c>
-      <c r="B100" t="s">
-        <v>563</v>
-      </c>
-      <c r="C100" t="s">
-        <v>564</v>
-      </c>
-      <c r="E100" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+      <c r="B108" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B101" t="s">
-        <v>565</v>
-      </c>
-      <c r="C101" t="s">
-        <v>566</v>
-      </c>
-      <c r="E101" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>325</v>
-      </c>
-      <c r="B102" t="s">
-        <v>567</v>
-      </c>
-      <c r="C102" t="s">
-        <v>568</v>
-      </c>
-      <c r="E102" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>385</v>
-      </c>
-      <c r="B103" t="s">
-        <v>569</v>
-      </c>
-      <c r="C103" t="s">
-        <v>570</v>
-      </c>
-      <c r="E103" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>310</v>
-      </c>
-      <c r="B104" t="s">
-        <v>571</v>
-      </c>
-      <c r="C104" t="s">
-        <v>549</v>
-      </c>
-      <c r="E104" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>356</v>
-      </c>
-      <c r="B105" t="s">
-        <v>572</v>
-      </c>
-      <c r="C105" t="s">
-        <v>573</v>
-      </c>
-      <c r="E105" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>312</v>
-      </c>
-      <c r="B106" t="s">
-        <v>574</v>
-      </c>
-      <c r="C106" t="s">
-        <v>575</v>
-      </c>
-      <c r="E106" t="s">
-        <v>113</v>
-      </c>
+      <c r="B109" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E222" s="3"/>
+    </row>
+    <row r="223" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E227" s="3"/>
+    </row>
+    <row r="228" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E229" s="3"/>
+    </row>
+    <row r="230" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E244" s="3"/>
+    </row>
+    <row r="245" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E245" s="3"/>
+    </row>
+    <row r="246" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E246" s="3"/>
+    </row>
+    <row r="247" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E247" s="3"/>
+    </row>
+    <row r="248" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E248" s="3"/>
+    </row>
+    <row r="249" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E250" s="3"/>
+    </row>
+    <row r="251" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E251" s="3"/>
+    </row>
+    <row r="252" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E252" s="3"/>
+    </row>
+    <row r="253" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E253" s="3"/>
+    </row>
+    <row r="254" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E254" s="3"/>
+    </row>
+    <row r="255" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E255" s="3"/>
+    </row>
+    <row r="256" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E257" s="3"/>
+    </row>
+    <row r="258" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E258" s="3"/>
+    </row>
+    <row r="259" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E259" s="3"/>
+    </row>
+    <row r="260" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E260" s="3"/>
+    </row>
+    <row r="261" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E261" s="3"/>
+    </row>
+    <row r="262" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E262" s="3"/>
+    </row>
+    <row r="263" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E263" s="3"/>
+    </row>
+    <row r="264" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E264" s="3"/>
+    </row>
+    <row r="265" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E265" s="3"/>
+    </row>
+    <row r="266" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E266" s="3"/>
+    </row>
+    <row r="267" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E267" s="3"/>
+    </row>
+    <row r="268" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E268" s="3"/>
+    </row>
+    <row r="269" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E269" s="3"/>
+    </row>
+    <row r="270" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E270" s="3"/>
+    </row>
+    <row r="271" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E271" s="3"/>
+    </row>
+    <row r="272" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E272" s="3"/>
+    </row>
+    <row r="273" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E273" s="3"/>
+    </row>
+    <row r="274" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E274" s="3"/>
+    </row>
+    <row r="275" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E275" s="3"/>
+    </row>
+    <row r="276" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E276" s="3"/>
+    </row>
+    <row r="277" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E277" s="3"/>
+    </row>
+    <row r="278" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E278" s="3"/>
+    </row>
+    <row r="279" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E279" s="3"/>
+    </row>
+    <row r="280" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E280" s="3"/>
+    </row>
+    <row r="281" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E281" s="3"/>
+    </row>
+    <row r="282" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E282" s="3"/>
+    </row>
+    <row r="283" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E283" s="3"/>
+    </row>
+    <row r="284" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E284" s="3"/>
+    </row>
+    <row r="285" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E285" s="3"/>
+    </row>
+    <row r="286" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E286" s="3"/>
+    </row>
+    <row r="287" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E287" s="3"/>
+    </row>
+    <row r="288" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E288" s="3"/>
+    </row>
+    <row r="289" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E289" s="3"/>
+    </row>
+    <row r="290" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E290" s="3"/>
+    </row>
+    <row r="291" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E291" s="3"/>
+    </row>
+    <row r="292" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E292" s="3"/>
+    </row>
+    <row r="293" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E293" s="3"/>
+    </row>
+    <row r="294" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E294" s="3"/>
+    </row>
+    <row r="295" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E295" s="3"/>
+    </row>
+    <row r="296" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E296" s="3"/>
+    </row>
+    <row r="297" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E297" s="3"/>
+    </row>
+    <row r="298" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E298" s="3"/>
+    </row>
+    <row r="299" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E299" s="3"/>
+    </row>
+    <row r="300" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E300" s="3"/>
+    </row>
+    <row r="301" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E301" s="3"/>
+    </row>
+    <row r="302" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E302" s="3"/>
+    </row>
+    <row r="303" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E303" s="3"/>
+    </row>
+    <row r="304" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E304" s="3"/>
+    </row>
+    <row r="305" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E305" s="3"/>
+    </row>
+    <row r="306" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E306" s="3"/>
+    </row>
+    <row r="307" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E307" s="3"/>
+    </row>
+    <row r="308" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E308" s="3"/>
+    </row>
+    <row r="309" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E309" s="3"/>
+    </row>
+    <row r="310" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E310" s="3"/>
+    </row>
+    <row r="311" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E311" s="3"/>
+    </row>
+    <row r="312" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E312" s="3"/>
+    </row>
+    <row r="313" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E313" s="3"/>
+    </row>
+    <row r="314" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E314" s="3"/>
+    </row>
+    <row r="315" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E315" s="3"/>
+    </row>
+    <row r="316" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E316" s="3"/>
+    </row>
+    <row r="317" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E317" s="3"/>
+    </row>
+    <row r="318" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E318" s="3"/>
+    </row>
+    <row r="319" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E319" s="3"/>
+    </row>
+    <row r="320" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E320" s="3"/>
+    </row>
+    <row r="321" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E321" s="3"/>
+    </row>
+    <row r="322" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E322" s="3"/>
+    </row>
+    <row r="323" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E323" s="3"/>
+    </row>
+    <row r="324" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E324" s="3"/>
+    </row>
+    <row r="325" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E325" s="3"/>
+    </row>
+    <row r="326" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E326" s="3"/>
+    </row>
+    <row r="327" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E327" s="3"/>
+    </row>
+    <row r="328" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E328" s="3"/>
+    </row>
+    <row r="329" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E329" s="3"/>
+    </row>
+    <row r="330" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E330" s="3"/>
+    </row>
+    <row r="331" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E331" s="3"/>
+    </row>
+    <row r="332" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E332" s="3"/>
+    </row>
+    <row r="333" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E333" s="3"/>
+    </row>
+    <row r="334" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E334" s="3"/>
+    </row>
+    <row r="335" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E335" s="3"/>
+    </row>
+    <row r="336" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E336" s="3"/>
+    </row>
+    <row r="337" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E337" s="3"/>
+    </row>
+    <row r="338" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E338" s="3"/>
+    </row>
+    <row r="339" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E339" s="3"/>
+    </row>
+    <row r="340" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E340" s="3"/>
+    </row>
+    <row r="341" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E341" s="3"/>
+    </row>
+    <row r="342" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E342" s="3"/>
+    </row>
+    <row r="343" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E343" s="3"/>
+    </row>
+    <row r="344" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E344" s="3"/>
+    </row>
+    <row r="345" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E345" s="3"/>
+    </row>
+    <row r="346" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E346" s="3"/>
+    </row>
+    <row r="347" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E347" s="3"/>
+    </row>
+    <row r="348" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E348" s="3"/>
+    </row>
+    <row r="349" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E349" s="3"/>
+    </row>
+    <row r="350" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E350" s="3"/>
+    </row>
+    <row r="351" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E351" s="3"/>
+    </row>
+    <row r="352" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E352" s="3"/>
+    </row>
+    <row r="353" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E353" s="3"/>
+    </row>
+    <row r="354" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E354" s="3"/>
+    </row>
+    <row r="355" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E355" s="3"/>
+    </row>
+    <row r="356" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E356" s="3"/>
+    </row>
+    <row r="357" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E357" s="3"/>
+    </row>
+    <row r="358" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E358" s="3"/>
+    </row>
+    <row r="359" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E359" s="3"/>
+    </row>
+    <row r="360" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E360" s="3"/>
+    </row>
+    <row r="361" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E361" s="3"/>
+    </row>
+    <row r="362" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E362" s="3"/>
+    </row>
+    <row r="363" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E363" s="3"/>
+    </row>
+    <row r="364" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E364" s="3"/>
+    </row>
+    <row r="365" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E365" s="3"/>
+    </row>
+    <row r="366" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E366" s="3"/>
+    </row>
+    <row r="367" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E367" s="3"/>
+    </row>
+    <row r="368" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E368" s="3"/>
+    </row>
+    <row r="369" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E369" s="3"/>
+    </row>
+    <row r="370" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E370" s="3"/>
+    </row>
+    <row r="371" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E371" s="3"/>
+    </row>
+    <row r="372" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E372" s="3"/>
+    </row>
+    <row r="373" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E373" s="3"/>
+    </row>
+    <row r="374" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E374" s="3"/>
+    </row>
+    <row r="375" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E375" s="3"/>
+    </row>
+    <row r="376" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E376" s="3"/>
+    </row>
+    <row r="377" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E377" s="3"/>
+    </row>
+    <row r="378" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E378" s="3"/>
+    </row>
+    <row r="379" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E379" s="3"/>
+    </row>
+    <row r="380" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E380" s="3"/>
+    </row>
+    <row r="381" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E381" s="3"/>
+    </row>
+    <row r="382" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E382" s="3"/>
+    </row>
+    <row r="383" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E383" s="3"/>
+    </row>
+    <row r="384" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E384" s="3"/>
+    </row>
+    <row r="385" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E385" s="3"/>
+    </row>
+    <row r="386" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E386" s="3"/>
+    </row>
+    <row r="387" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E387" s="3"/>
+    </row>
+    <row r="388" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E388" s="3"/>
+    </row>
+    <row r="389" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E389" s="3"/>
+    </row>
+    <row r="390" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E390" s="3"/>
+    </row>
+    <row r="391" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E391" s="3"/>
+    </row>
+    <row r="392" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E392" s="3"/>
+    </row>
+    <row r="393" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E393" s="3"/>
+    </row>
+    <row r="394" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E394" s="3"/>
+    </row>
+    <row r="395" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E395" s="3"/>
+    </row>
+    <row r="396" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E396" s="3"/>
+    </row>
+    <row r="397" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E397" s="3"/>
+    </row>
+    <row r="398" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E398" s="3"/>
+    </row>
+    <row r="399" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E399" s="3"/>
+    </row>
+    <row r="400" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E400" s="3"/>
+    </row>
+    <row r="401" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E401" s="3"/>
+    </row>
+    <row r="402" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E402" s="3"/>
+    </row>
+    <row r="403" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E403" s="3"/>
+    </row>
+    <row r="404" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E404" s="3"/>
+    </row>
+    <row r="405" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E405" s="3"/>
+    </row>
+    <row r="406" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E406" s="3"/>
+    </row>
+    <row r="407" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E407" s="3"/>
+    </row>
+    <row r="408" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E408" s="3"/>
+    </row>
+    <row r="409" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E409" s="3"/>
+    </row>
+    <row r="410" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E410" s="3"/>
+    </row>
+    <row r="411" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E411" s="3"/>
+    </row>
+    <row r="412" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E412" s="3"/>
+    </row>
+    <row r="413" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E413" s="3"/>
+    </row>
+    <row r="414" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E414" s="3"/>
+    </row>
+    <row r="415" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E415" s="3"/>
+    </row>
+    <row r="416" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E416" s="3"/>
+    </row>
+    <row r="417" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E417" s="3"/>
+    </row>
+    <row r="418" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E418" s="3"/>
+    </row>
+    <row r="419" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E419" s="3"/>
+    </row>
+    <row r="420" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E420" s="3"/>
+    </row>
+    <row r="421" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E421" s="3"/>
+    </row>
+    <row r="422" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E422" s="3"/>
+    </row>
+    <row r="423" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E423" s="3"/>
+    </row>
+    <row r="424" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E424" s="3"/>
+    </row>
+    <row r="425" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E425" s="3"/>
+    </row>
+    <row r="426" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E426" s="3"/>
+    </row>
+    <row r="427" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E427" s="3"/>
+    </row>
+    <row r="428" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E428" s="3"/>
+    </row>
+    <row r="429" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E429" s="3"/>
+    </row>
+    <row r="430" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E430" s="3"/>
+    </row>
+    <row r="431" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E431" s="3"/>
+    </row>
+    <row r="432" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E432" s="3"/>
+    </row>
+    <row r="433" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E433" s="3"/>
+    </row>
+    <row r="434" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E434" s="3"/>
+    </row>
+    <row r="435" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E435" s="3"/>
+    </row>
+    <row r="436" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E436" s="3"/>
+    </row>
+    <row r="437" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E437" s="3"/>
+    </row>
+    <row r="438" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E438" s="3"/>
+    </row>
+    <row r="439" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E439" s="3"/>
+    </row>
+    <row r="440" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E440" s="3"/>
+    </row>
+    <row r="441" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E441" s="3"/>
+    </row>
+    <row r="442" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E442" s="3"/>
+    </row>
+    <row r="443" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E443" s="3"/>
+    </row>
+    <row r="444" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E444" s="3"/>
+    </row>
+    <row r="445" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E445" s="3"/>
+    </row>
+    <row r="446" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E446" s="3"/>
+    </row>
+    <row r="447" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E447" s="3"/>
+    </row>
+    <row r="448" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E448" s="3"/>
+    </row>
+    <row r="449" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E449" s="3"/>
+    </row>
+    <row r="450" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E450" s="3"/>
+    </row>
+    <row r="451" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E451" s="3"/>
+    </row>
+    <row r="452" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E452" s="3"/>
+    </row>
+    <row r="453" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E453" s="3"/>
+    </row>
+    <row r="454" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E454" s="3"/>
+    </row>
+    <row r="455" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E455" s="3"/>
+    </row>
+    <row r="456" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E456" s="3"/>
+    </row>
+    <row r="457" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E457" s="3"/>
+    </row>
+    <row r="458" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E458" s="3"/>
+    </row>
+    <row r="459" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E459" s="3"/>
+    </row>
+    <row r="460" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E460" s="3"/>
+    </row>
+    <row r="461" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E461" s="3"/>
+    </row>
+    <row r="462" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E462" s="3"/>
+    </row>
+    <row r="463" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E463" s="3"/>
+    </row>
+    <row r="464" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E464" s="3"/>
+    </row>
+    <row r="465" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E465" s="3"/>
+    </row>
+    <row r="466" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E466" s="3"/>
+    </row>
+    <row r="467" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E467" s="3"/>
+    </row>
+    <row r="468" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E468" s="3"/>
+    </row>
+    <row r="469" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E469" s="3"/>
+    </row>
+    <row r="470" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E470" s="3"/>
+    </row>
+    <row r="471" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E471" s="3"/>
+    </row>
+    <row r="472" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E472" s="3"/>
+    </row>
+    <row r="473" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E473" s="3"/>
+    </row>
+    <row r="474" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E474" s="3"/>
+    </row>
+    <row r="475" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E475" s="3"/>
+    </row>
+    <row r="476" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E476" s="3"/>
+    </row>
+    <row r="477" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E477" s="3"/>
+    </row>
+    <row r="478" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E478" s="3"/>
+    </row>
+    <row r="479" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E479" s="3"/>
+    </row>
+    <row r="480" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E480" s="3"/>
+    </row>
+    <row r="481" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E481" s="3"/>
+    </row>
+    <row r="482" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E482" s="3"/>
+    </row>
+    <row r="483" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E483" s="3"/>
+    </row>
+    <row r="484" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E484" s="3"/>
+    </row>
+    <row r="485" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E485" s="3"/>
+    </row>
+    <row r="486" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E486" s="3"/>
+    </row>
+    <row r="487" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E487" s="3"/>
+    </row>
+    <row r="488" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E488" s="3"/>
+    </row>
+    <row r="489" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E489" s="3"/>
+    </row>
+    <row r="490" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E490" s="3"/>
+    </row>
+    <row r="491" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E491" s="3"/>
+    </row>
+    <row r="492" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E492" s="3"/>
+    </row>
+    <row r="493" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E493" s="3"/>
+    </row>
+    <row r="494" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E494" s="3"/>
+    </row>
+    <row r="495" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E495" s="3"/>
+    </row>
+    <row r="496" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E496" s="3"/>
+    </row>
+    <row r="497" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E497" s="3"/>
+    </row>
+    <row r="498" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E498" s="3"/>
+    </row>
+    <row r="499" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E499" s="3"/>
+    </row>
+    <row r="500" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E500" s="3"/>
+    </row>
+    <row r="501" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E501" s="3"/>
+    </row>
+    <row r="502" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E502" s="3"/>
+    </row>
+    <row r="503" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E503" s="3"/>
+    </row>
+    <row r="504" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E504" s="3"/>
+    </row>
+    <row r="505" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E505" s="3"/>
+    </row>
+    <row r="506" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E506" s="3"/>
+    </row>
+    <row r="507" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E507" s="3"/>
+    </row>
+    <row r="508" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E508" s="3"/>
+    </row>
+    <row r="509" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E509" s="3"/>
+    </row>
+    <row r="510" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E510" s="3"/>
+    </row>
+    <row r="511" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E511" s="3"/>
+    </row>
+    <row r="512" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E512" s="3"/>
+    </row>
+    <row r="513" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E513" s="3"/>
+    </row>
+    <row r="514" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E514" s="3"/>
+    </row>
+    <row r="515" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E515" s="3"/>
+    </row>
+    <row r="516" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E516" s="3"/>
+    </row>
+    <row r="517" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E517" s="3"/>
+    </row>
+    <row r="518" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E518" s="3"/>
+    </row>
+    <row r="519" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E519" s="3"/>
+    </row>
+    <row r="520" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E520" s="3"/>
+    </row>
+    <row r="521" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E521" s="3"/>
+    </row>
+    <row r="522" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E522" s="3"/>
+    </row>
+    <row r="523" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E523" s="3"/>
+    </row>
+    <row r="524" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E524" s="3"/>
+    </row>
+    <row r="525" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E525" s="3"/>
+    </row>
+    <row r="526" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E526" s="3"/>
+    </row>
+    <row r="527" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E527" s="3"/>
+    </row>
+    <row r="528" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E528" s="3"/>
+    </row>
+    <row r="529" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E529" s="3"/>
+    </row>
+    <row r="530" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E530" s="3"/>
+    </row>
+    <row r="531" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E531" s="3"/>
+    </row>
+    <row r="532" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E532" s="3"/>
+    </row>
+    <row r="533" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E533" s="3"/>
+    </row>
+    <row r="534" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E534" s="3"/>
+    </row>
+    <row r="535" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E535" s="3"/>
+    </row>
+    <row r="536" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E536" s="3"/>
+    </row>
+    <row r="537" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E537" s="3"/>
+    </row>
+    <row r="538" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E538" s="3"/>
+    </row>
+    <row r="539" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E539" s="3"/>
+    </row>
+    <row r="540" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E540" s="3"/>
+    </row>
+    <row r="541" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E541" s="3"/>
+    </row>
+    <row r="542" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E542" s="3"/>
+    </row>
+    <row r="543" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E543" s="3"/>
+    </row>
+    <row r="544" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E544" s="3"/>
+    </row>
+    <row r="545" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E545" s="3"/>
+    </row>
+    <row r="546" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E546" s="3"/>
+    </row>
+    <row r="547" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E547" s="3"/>
+    </row>
+    <row r="548" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E548" s="3"/>
+    </row>
+    <row r="549" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E549" s="3"/>
+    </row>
+    <row r="550" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E550" s="3"/>
+    </row>
+    <row r="551" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E551" s="3"/>
+    </row>
+    <row r="552" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E552" s="3"/>
+    </row>
+    <row r="553" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E553" s="3"/>
+    </row>
+    <row r="554" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E554" s="3"/>
+    </row>
+    <row r="555" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E555" s="3"/>
+    </row>
+    <row r="556" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E556" s="3"/>
+    </row>
+    <row r="557" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E557" s="3"/>
+    </row>
+    <row r="558" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E558" s="3"/>
+    </row>
+    <row r="559" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E559" s="3"/>
+    </row>
+    <row r="560" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E560" s="3"/>
+    </row>
+    <row r="561" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E561" s="3"/>
+    </row>
+    <row r="562" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E562" s="3"/>
+    </row>
+    <row r="563" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E563" s="3"/>
+    </row>
+    <row r="564" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E564" s="3"/>
+    </row>
+    <row r="565" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E565" s="3"/>
+    </row>
+    <row r="566" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E566" s="3"/>
+    </row>
+    <row r="567" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E567" s="3"/>
+    </row>
+    <row r="568" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E568" s="3"/>
+    </row>
+    <row r="569" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E569" s="3"/>
+    </row>
+    <row r="570" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E570" s="3"/>
+    </row>
+    <row r="571" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E571" s="3"/>
+    </row>
+    <row r="572" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E572" s="3"/>
+    </row>
+    <row r="573" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E573" s="3"/>
+    </row>
+    <row r="574" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E574" s="3"/>
+    </row>
+    <row r="575" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E575" s="3"/>
+    </row>
+    <row r="576" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E576" s="3"/>
+    </row>
+    <row r="577" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E577" s="3"/>
+    </row>
+    <row r="578" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E578" s="3"/>
+    </row>
+    <row r="579" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E579" s="3"/>
+    </row>
+    <row r="580" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E580" s="3"/>
+    </row>
+    <row r="581" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E581" s="3"/>
+    </row>
+    <row r="582" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E582" s="3"/>
+    </row>
+    <row r="583" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E583" s="3"/>
+    </row>
+    <row r="584" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E584" s="3"/>
+    </row>
+    <row r="585" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E585" s="3"/>
+    </row>
+    <row r="586" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E586" s="3"/>
+    </row>
+    <row r="587" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E587" s="3"/>
+    </row>
+    <row r="588" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E588" s="3"/>
+    </row>
+    <row r="589" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E589" s="3"/>
+    </row>
+    <row r="590" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E590" s="3"/>
+    </row>
+    <row r="591" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E591" s="3"/>
+    </row>
+    <row r="592" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E592" s="3"/>
+    </row>
+    <row r="593" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E593" s="3"/>
+    </row>
+    <row r="594" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E594" s="3"/>
+    </row>
+    <row r="595" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E595" s="3"/>
+    </row>
+    <row r="596" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E596" s="3"/>
+    </row>
+    <row r="597" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E597" s="3"/>
+    </row>
+    <row r="598" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E598" s="3"/>
+    </row>
+    <row r="599" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E599" s="3"/>
+    </row>
+    <row r="600" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E600" s="3"/>
+    </row>
+    <row r="601" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E601" s="3"/>
+    </row>
+    <row r="602" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E602" s="3"/>
+    </row>
+    <row r="603" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E603" s="3"/>
+    </row>
+    <row r="604" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E604" s="3"/>
+    </row>
+    <row r="605" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E605" s="3"/>
+    </row>
+    <row r="606" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E606" s="3"/>
+    </row>
+    <row r="607" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E607" s="3"/>
+    </row>
+    <row r="608" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E608" s="3"/>
+    </row>
+    <row r="609" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E609" s="3"/>
+    </row>
+    <row r="610" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E610" s="3"/>
+    </row>
+    <row r="611" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E611" s="3"/>
+    </row>
+    <row r="612" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E612" s="3"/>
+    </row>
+    <row r="613" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E613" s="3"/>
+    </row>
+    <row r="614" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E614" s="3"/>
+    </row>
+    <row r="615" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E615" s="3"/>
+    </row>
+    <row r="616" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E616" s="3"/>
+    </row>
+    <row r="617" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E617" s="3"/>
+    </row>
+    <row r="618" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E618" s="3"/>
+    </row>
+    <row r="619" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E619" s="3"/>
+    </row>
+    <row r="620" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E620" s="3"/>
+    </row>
+    <row r="621" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E621" s="3"/>
+    </row>
+    <row r="622" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E622" s="3"/>
+    </row>
+    <row r="623" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E623" s="3"/>
+    </row>
+    <row r="624" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E624" s="3"/>
+    </row>
+    <row r="625" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E625" s="3"/>
+    </row>
+    <row r="626" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E626" s="3"/>
+    </row>
+    <row r="627" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E627" s="3"/>
+    </row>
+    <row r="628" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E628" s="3"/>
+    </row>
+    <row r="629" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E629" s="3"/>
+    </row>
+    <row r="630" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E630" s="3"/>
+    </row>
+    <row r="631" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E631" s="3"/>
+    </row>
+    <row r="632" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E632" s="3"/>
+    </row>
+    <row r="633" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E633" s="3"/>
+    </row>
+    <row r="634" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E634" s="3"/>
+    </row>
+    <row r="635" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E635" s="3"/>
+    </row>
+    <row r="636" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E636" s="3"/>
+    </row>
+    <row r="637" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E637" s="3"/>
+    </row>
+    <row r="638" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E638" s="3"/>
+    </row>
+    <row r="639" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E639" s="3"/>
+    </row>
+    <row r="640" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E640" s="3"/>
+    </row>
+    <row r="641" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E641" s="3"/>
+    </row>
+    <row r="642" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E642" s="3"/>
+    </row>
+    <row r="643" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E643" s="3"/>
+    </row>
+    <row r="644" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E644" s="3"/>
+    </row>
+    <row r="645" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E645" s="3"/>
+    </row>
+    <row r="646" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E646" s="3"/>
+    </row>
+    <row r="647" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E647" s="3"/>
+    </row>
+    <row r="648" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E648" s="3"/>
+    </row>
+    <row r="649" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E649" s="3"/>
+    </row>
+    <row r="650" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E650" s="3"/>
+    </row>
+    <row r="651" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E651" s="3"/>
+    </row>
+    <row r="652" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E652" s="3"/>
+    </row>
+    <row r="653" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E653" s="3"/>
+    </row>
+    <row r="654" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E654" s="3"/>
+    </row>
+    <row r="655" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E655" s="3"/>
+    </row>
+    <row r="656" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E656" s="3"/>
+    </row>
+    <row r="657" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E657" s="3"/>
+    </row>
+    <row r="658" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E658" s="3"/>
+    </row>
+    <row r="659" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E659" s="3"/>
+    </row>
+    <row r="660" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E660" s="3"/>
+    </row>
+    <row r="661" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E661" s="3"/>
+    </row>
+    <row r="662" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E662" s="3"/>
+    </row>
+    <row r="663" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E663" s="3"/>
+    </row>
+    <row r="664" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E664" s="3"/>
+    </row>
+    <row r="665" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E665" s="3"/>
+    </row>
+    <row r="666" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E666" s="3"/>
+    </row>
+    <row r="667" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E667" s="3"/>
+    </row>
+    <row r="668" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E668" s="3"/>
+    </row>
+    <row r="669" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E669" s="3"/>
+    </row>
+    <row r="670" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E670" s="3"/>
+    </row>
+    <row r="671" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E671" s="3"/>
+    </row>
+    <row r="672" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E672" s="3"/>
+    </row>
+    <row r="673" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E673" s="3"/>
+    </row>
+    <row r="674" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E674" s="3"/>
+    </row>
+    <row r="675" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E675" s="3"/>
+    </row>
+    <row r="676" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E676" s="3"/>
+    </row>
+    <row r="677" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E677" s="3"/>
+    </row>
+    <row r="678" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E678" s="3"/>
+    </row>
+    <row r="679" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E679" s="3"/>
+    </row>
+    <row r="680" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E680" s="3"/>
+    </row>
+    <row r="681" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E681" s="3"/>
+    </row>
+    <row r="682" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E682" s="3"/>
+    </row>
+    <row r="683" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E683" s="3"/>
+    </row>
+    <row r="684" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E684" s="3"/>
+    </row>
+    <row r="685" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E685" s="3"/>
+    </row>
+    <row r="686" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E686" s="3"/>
+    </row>
+    <row r="687" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E687" s="3"/>
+    </row>
+    <row r="688" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E688" s="3"/>
+    </row>
+    <row r="689" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E689" s="3"/>
+    </row>
+    <row r="690" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E690" s="3"/>
+    </row>
+    <row r="691" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E691" s="3"/>
+    </row>
+    <row r="692" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E692" s="3"/>
+    </row>
+    <row r="693" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E693" s="3"/>
+    </row>
+    <row r="694" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E694" s="3"/>
+    </row>
+    <row r="695" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E695" s="3"/>
+    </row>
+    <row r="696" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E696" s="3"/>
+    </row>
+    <row r="697" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E697" s="3"/>
+    </row>
+    <row r="698" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E698" s="3"/>
+    </row>
+    <row r="699" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E699" s="3"/>
+    </row>
+    <row r="700" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E700" s="3"/>
+    </row>
+    <row r="701" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E701" s="3"/>
+    </row>
+    <row r="702" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E702" s="3"/>
+    </row>
+    <row r="703" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E703" s="3"/>
+    </row>
+    <row r="704" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E704" s="3"/>
+    </row>
+    <row r="705" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E705" s="3"/>
+    </row>
+    <row r="706" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E706" s="3"/>
+    </row>
+    <row r="707" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E707" s="3"/>
+    </row>
+    <row r="708" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E708" s="3"/>
+    </row>
+    <row r="709" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E709" s="3"/>
+    </row>
+    <row r="710" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E710" s="3"/>
+    </row>
+    <row r="711" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E711" s="3"/>
+    </row>
+    <row r="712" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E712" s="3"/>
+    </row>
+    <row r="713" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E713" s="3"/>
+    </row>
+    <row r="714" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E714" s="3"/>
+    </row>
+    <row r="715" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E715" s="3"/>
+    </row>
+    <row r="716" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E716" s="3"/>
+    </row>
+    <row r="717" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E717" s="3"/>
+    </row>
+    <row r="718" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E718" s="3"/>
+    </row>
+    <row r="719" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E719" s="3"/>
+    </row>
+    <row r="720" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E720" s="3"/>
+    </row>
+    <row r="721" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E721" s="3"/>
+    </row>
+    <row r="722" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E722" s="3"/>
+    </row>
+    <row r="723" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E723" s="3"/>
+    </row>
+    <row r="724" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E724" s="3"/>
+    </row>
+    <row r="725" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E725" s="3"/>
+    </row>
+    <row r="726" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E726" s="3"/>
+    </row>
+    <row r="727" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E727" s="3"/>
+    </row>
+    <row r="728" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E728" s="3"/>
+    </row>
+    <row r="729" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E729" s="3"/>
+    </row>
+    <row r="730" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E730" s="3"/>
+    </row>
+    <row r="731" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E731" s="3"/>
+    </row>
+    <row r="732" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E732" s="3"/>
+    </row>
+    <row r="733" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E733" s="3"/>
+    </row>
+    <row r="734" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E734" s="3"/>
+    </row>
+    <row r="735" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E735" s="3"/>
+    </row>
+    <row r="736" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E736" s="3"/>
+    </row>
+    <row r="737" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E737" s="3"/>
+    </row>
+    <row r="738" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E738" s="3"/>
+    </row>
+    <row r="739" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E739" s="3"/>
+    </row>
+    <row r="740" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E740" s="3"/>
+    </row>
+    <row r="741" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E741" s="3"/>
+    </row>
+    <row r="742" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E742" s="3"/>
+    </row>
+    <row r="743" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E743" s="3"/>
+    </row>
+    <row r="744" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E744" s="3"/>
+    </row>
+    <row r="745" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E745" s="3"/>
+    </row>
+    <row r="746" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E746" s="3"/>
+    </row>
+    <row r="747" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E747" s="3"/>
+    </row>
+    <row r="748" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E748" s="3"/>
+    </row>
+    <row r="749" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E749" s="3"/>
+    </row>
+    <row r="750" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E750" s="3"/>
+    </row>
+    <row r="751" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E751" s="3"/>
+    </row>
+    <row r="752" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E752" s="3"/>
+    </row>
+    <row r="753" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E753" s="3"/>
+    </row>
+    <row r="754" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E754" s="3"/>
+    </row>
+    <row r="755" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E755" s="3"/>
+    </row>
+    <row r="756" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E756" s="3"/>
+    </row>
+    <row r="757" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E757" s="3"/>
+    </row>
+    <row r="758" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E758" s="3"/>
+    </row>
+    <row r="759" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E759" s="3"/>
+    </row>
+    <row r="760" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E760" s="3"/>
+    </row>
+    <row r="761" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E761" s="3"/>
+    </row>
+    <row r="762" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E762" s="3"/>
+    </row>
+    <row r="763" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E763" s="3"/>
+    </row>
+    <row r="764" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E764" s="3"/>
+    </row>
+    <row r="765" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E765" s="3"/>
+    </row>
+    <row r="766" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E766" s="3"/>
+    </row>
+    <row r="767" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E767" s="3"/>
+    </row>
+    <row r="768" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E768" s="3"/>
+    </row>
+    <row r="769" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E769" s="3"/>
+    </row>
+    <row r="770" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E770" s="3"/>
+    </row>
+    <row r="771" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E771" s="3"/>
+    </row>
+    <row r="772" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E772" s="3"/>
+    </row>
+    <row r="773" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E773" s="3"/>
+    </row>
+    <row r="774" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E774" s="3"/>
+    </row>
+    <row r="775" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E775" s="3"/>
+    </row>
+    <row r="776" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E776" s="3"/>
+    </row>
+    <row r="777" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E777" s="3"/>
+    </row>
+    <row r="778" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E778" s="3"/>
+    </row>
+    <row r="779" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E779" s="3"/>
+    </row>
+    <row r="780" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E780" s="3"/>
+    </row>
+    <row r="781" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E781" s="3"/>
+    </row>
+    <row r="782" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E782" s="3"/>
+    </row>
+    <row r="783" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E783" s="3"/>
+    </row>
+    <row r="784" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E784" s="3"/>
+    </row>
+    <row r="785" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E785" s="3"/>
+    </row>
+    <row r="786" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E786" s="3"/>
+    </row>
+    <row r="787" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E787" s="3"/>
+    </row>
+    <row r="788" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E788" s="3"/>
+    </row>
+    <row r="789" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E789" s="3"/>
+    </row>
+    <row r="790" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E790" s="3"/>
+    </row>
+    <row r="791" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E791" s="3"/>
+    </row>
+    <row r="792" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E792" s="3"/>
+    </row>
+    <row r="793" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E793" s="3"/>
+    </row>
+    <row r="794" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E794" s="3"/>
+    </row>
+    <row r="795" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E795" s="3"/>
+    </row>
+    <row r="796" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E796" s="3"/>
+    </row>
+    <row r="797" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E797" s="3"/>
+    </row>
+    <row r="798" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E798" s="3"/>
+    </row>
+    <row r="799" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E799" s="3"/>
+    </row>
+    <row r="800" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E800" s="3"/>
+    </row>
+    <row r="801" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E801" s="3"/>
+    </row>
+    <row r="802" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E802" s="3"/>
+    </row>
+    <row r="803" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E803" s="3"/>
+    </row>
+    <row r="804" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E804" s="3"/>
+    </row>
+    <row r="805" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E805" s="3"/>
+    </row>
+    <row r="806" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E806" s="3"/>
+    </row>
+    <row r="807" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E807" s="3"/>
+    </row>
+    <row r="808" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E808" s="3"/>
+    </row>
+    <row r="809" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E809" s="3"/>
+    </row>
+    <row r="810" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E810" s="3"/>
+    </row>
+    <row r="811" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E811" s="3"/>
+    </row>
+    <row r="812" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E812" s="3"/>
+    </row>
+    <row r="813" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E813" s="3"/>
+    </row>
+    <row r="814" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E814" s="3"/>
+    </row>
+    <row r="815" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E815" s="3"/>
+    </row>
+    <row r="816" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E816" s="3"/>
+    </row>
+    <row r="817" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E817" s="3"/>
+    </row>
+    <row r="818" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E818" s="3"/>
+    </row>
+    <row r="819" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E819" s="3"/>
+    </row>
+    <row r="820" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E820" s="3"/>
+    </row>
+    <row r="821" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E821" s="3"/>
+    </row>
+    <row r="822" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E822" s="3"/>
+    </row>
+    <row r="823" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E823" s="3"/>
+    </row>
+    <row r="824" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E824" s="3"/>
+    </row>
+    <row r="825" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E825" s="3"/>
+    </row>
+    <row r="826" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E826" s="3"/>
+    </row>
+    <row r="827" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E827" s="3"/>
+    </row>
+    <row r="828" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E828" s="3"/>
+    </row>
+    <row r="829" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E829" s="3"/>
+    </row>
+    <row r="830" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E830" s="3"/>
+    </row>
+    <row r="831" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E831" s="3"/>
+    </row>
+    <row r="832" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E832" s="3"/>
+    </row>
+    <row r="833" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E833" s="3"/>
+    </row>
+    <row r="834" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E834" s="3"/>
+    </row>
+    <row r="835" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E835" s="3"/>
+    </row>
+    <row r="836" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E836" s="3"/>
+    </row>
+    <row r="837" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E837" s="3"/>
+    </row>
+    <row r="838" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E838" s="3"/>
+    </row>
+    <row r="839" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E839" s="3"/>
+    </row>
+    <row r="840" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E840" s="3"/>
+    </row>
+    <row r="841" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E841" s="3"/>
+    </row>
+    <row r="842" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E842" s="3"/>
+    </row>
+    <row r="843" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E843" s="3"/>
+    </row>
+    <row r="844" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E844" s="3"/>
+    </row>
+    <row r="845" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E845" s="3"/>
+    </row>
+    <row r="846" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E846" s="3"/>
+    </row>
+    <row r="847" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E847" s="3"/>
+    </row>
+    <row r="848" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E848" s="3"/>
+    </row>
+    <row r="849" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E849" s="3"/>
+    </row>
+    <row r="850" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E850" s="3"/>
+    </row>
+    <row r="851" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E851" s="3"/>
+    </row>
+    <row r="852" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E852" s="3"/>
+    </row>
+    <row r="853" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E853" s="3"/>
+    </row>
+    <row r="854" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E854" s="3"/>
+    </row>
+    <row r="855" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E855" s="3"/>
+    </row>
+    <row r="856" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E856" s="3"/>
+    </row>
+    <row r="857" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E857" s="3"/>
+    </row>
+    <row r="858" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E858" s="3"/>
+    </row>
+    <row r="859" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E859" s="3"/>
+    </row>
+    <row r="860" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E860" s="3"/>
+    </row>
+    <row r="861" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E861" s="3"/>
+    </row>
+    <row r="862" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E862" s="3"/>
+    </row>
+    <row r="863" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E863" s="3"/>
+    </row>
+    <row r="864" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E864" s="3"/>
+    </row>
+    <row r="865" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E865" s="3"/>
+    </row>
+    <row r="866" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E866" s="3"/>
+    </row>
+    <row r="867" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E867" s="3"/>
+    </row>
+    <row r="868" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E868" s="3"/>
+    </row>
+    <row r="869" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E869" s="3"/>
+    </row>
+    <row r="870" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E870" s="3"/>
+    </row>
+    <row r="871" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E871" s="3"/>
+    </row>
+    <row r="872" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E872" s="3"/>
+    </row>
+    <row r="873" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E873" s="3"/>
+    </row>
+    <row r="874" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E874" s="3"/>
+    </row>
+    <row r="875" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E875" s="3"/>
+    </row>
+    <row r="876" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E876" s="3"/>
+    </row>
+    <row r="877" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E877" s="3"/>
+    </row>
+    <row r="878" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E878" s="3"/>
+    </row>
+    <row r="879" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E879" s="3"/>
+    </row>
+    <row r="880" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E880" s="3"/>
+    </row>
+    <row r="881" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E881" s="3"/>
+    </row>
+    <row r="882" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E882" s="3"/>
+    </row>
+    <row r="883" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E883" s="3"/>
+    </row>
+    <row r="884" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E884" s="3"/>
+    </row>
+    <row r="885" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E885" s="3"/>
+    </row>
+    <row r="886" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E886" s="3"/>
+    </row>
+    <row r="887" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E887" s="3"/>
+    </row>
+    <row r="888" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E888" s="3"/>
+    </row>
+    <row r="889" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E889" s="3"/>
+    </row>
+    <row r="890" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E890" s="3"/>
+    </row>
+    <row r="891" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E891" s="3"/>
+    </row>
+    <row r="892" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E892" s="3"/>
+    </row>
+    <row r="893" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E893" s="3"/>
+    </row>
+    <row r="894" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E894" s="3"/>
+    </row>
+    <row r="895" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E895" s="3"/>
+    </row>
+    <row r="896" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E896" s="3"/>
+    </row>
+    <row r="897" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E897" s="3"/>
+    </row>
+    <row r="898" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E898" s="3"/>
+    </row>
+    <row r="899" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E899" s="3"/>
+    </row>
+    <row r="900" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E900" s="3"/>
+    </row>
+    <row r="901" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E901" s="3"/>
+    </row>
+    <row r="902" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E902" s="3"/>
+    </row>
+    <row r="903" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E903" s="3"/>
+    </row>
+    <row r="904" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E904" s="3"/>
+    </row>
+    <row r="905" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E905" s="3"/>
+    </row>
+    <row r="906" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E906" s="3"/>
+    </row>
+    <row r="907" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E907" s="3"/>
+    </row>
+    <row r="908" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E908" s="3"/>
+    </row>
+    <row r="909" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E909" s="3"/>
+    </row>
+    <row r="910" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E910" s="3"/>
+    </row>
+    <row r="911" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E911" s="3"/>
+    </row>
+    <row r="912" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E912" s="3"/>
+    </row>
+    <row r="913" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E913" s="3"/>
+    </row>
+    <row r="914" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E914" s="3"/>
+    </row>
+    <row r="915" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E915" s="3"/>
+    </row>
+    <row r="916" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E916" s="3"/>
+    </row>
+    <row r="917" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E917" s="3"/>
+    </row>
+    <row r="918" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E918" s="3"/>
+    </row>
+    <row r="919" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E919" s="3"/>
+    </row>
+    <row r="920" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E920" s="3"/>
+    </row>
+    <row r="921" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E921" s="3"/>
+    </row>
+    <row r="922" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E922" s="3"/>
+    </row>
+    <row r="923" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E923" s="3"/>
+    </row>
+    <row r="924" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E924" s="3"/>
+    </row>
+    <row r="925" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E925" s="3"/>
+    </row>
+    <row r="926" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E926" s="3"/>
+    </row>
+    <row r="927" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E927" s="3"/>
+    </row>
+    <row r="928" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E928" s="3"/>
+    </row>
+    <row r="929" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E929" s="3"/>
+    </row>
+    <row r="930" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E930" s="3"/>
+    </row>
+    <row r="931" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E931" s="3"/>
+    </row>
+    <row r="932" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E932" s="3"/>
+    </row>
+    <row r="933" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E933" s="3"/>
+    </row>
+    <row r="934" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E934" s="3"/>
+    </row>
+    <row r="935" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E935" s="3"/>
+    </row>
+    <row r="936" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E936" s="3"/>
+    </row>
+    <row r="937" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E937" s="3"/>
+    </row>
+    <row r="938" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E938" s="3"/>
+    </row>
+    <row r="939" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E939" s="3"/>
+    </row>
+    <row r="940" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E940" s="3"/>
+    </row>
+    <row r="941" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E941" s="3"/>
+    </row>
+    <row r="942" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E942" s="3"/>
+    </row>
+    <row r="943" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E943" s="3"/>
+    </row>
+    <row r="944" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E944" s="3"/>
+    </row>
+    <row r="945" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E945" s="3"/>
+    </row>
+    <row r="946" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E946" s="3"/>
+    </row>
+    <row r="947" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E947" s="3"/>
+    </row>
+    <row r="948" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E948" s="3"/>
+    </row>
+    <row r="949" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E949" s="3"/>
+    </row>
+    <row r="950" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E950" s="3"/>
+    </row>
+    <row r="951" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E951" s="3"/>
+    </row>
+    <row r="952" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E952" s="3"/>
+    </row>
+    <row r="953" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E953" s="3"/>
+    </row>
+    <row r="954" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E954" s="3"/>
+    </row>
+    <row r="955" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E955" s="3"/>
+    </row>
+    <row r="956" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E956" s="3"/>
+    </row>
+    <row r="957" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E957" s="3"/>
+    </row>
+    <row r="958" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E958" s="3"/>
+    </row>
+    <row r="959" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E959" s="3"/>
+    </row>
+    <row r="960" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E960" s="3"/>
+    </row>
+    <row r="961" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E961" s="3"/>
+    </row>
+    <row r="962" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E962" s="3"/>
+    </row>
+    <row r="963" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E963" s="3"/>
+    </row>
+    <row r="964" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E964" s="3"/>
+    </row>
+    <row r="965" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E965" s="3"/>
+    </row>
+    <row r="966" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E966" s="3"/>
+    </row>
+    <row r="967" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E967" s="3"/>
+    </row>
+    <row r="968" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E968" s="3"/>
+    </row>
+    <row r="969" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E969" s="3"/>
+    </row>
+    <row r="970" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E970" s="3"/>
+    </row>
+    <row r="971" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E971" s="3"/>
+    </row>
+    <row r="972" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E972" s="3"/>
+    </row>
+    <row r="973" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E973" s="3"/>
+    </row>
+    <row r="974" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E974" s="3"/>
+    </row>
+    <row r="975" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E975" s="3"/>
+    </row>
+    <row r="976" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E976" s="3"/>
+    </row>
+    <row r="977" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E977" s="3"/>
+    </row>
+    <row r="978" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E978" s="3"/>
+    </row>
+    <row r="979" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E979" s="3"/>
+    </row>
+    <row r="980" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E980" s="3"/>
+    </row>
+    <row r="981" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E981" s="3"/>
+    </row>
+    <row r="982" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E982" s="3"/>
+    </row>
+    <row r="983" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E983" s="3"/>
+    </row>
+    <row r="984" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E984" s="3"/>
+    </row>
+    <row r="985" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E985" s="3"/>
+    </row>
+    <row r="986" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E986" s="3"/>
+    </row>
+    <row r="987" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E987" s="3"/>
+    </row>
+    <row r="988" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E988" s="3"/>
+    </row>
+    <row r="989" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E989" s="3"/>
+    </row>
+    <row r="990" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E990" s="3"/>
+    </row>
+    <row r="991" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E991" s="3"/>
+    </row>
+    <row r="992" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E992" s="3"/>
+    </row>
+    <row r="993" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E993" s="3"/>
+    </row>
+    <row r="994" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E994" s="3"/>
+    </row>
+    <row r="995" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E995" s="3"/>
+    </row>
+    <row r="996" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E996" s="3"/>
+    </row>
+    <row r="997" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E997" s="3"/>
+    </row>
+    <row r="998" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E998" s="3"/>
+    </row>
+    <row r="999" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E999" s="3"/>
+    </row>
+    <row r="1000" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E1000" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>